--- a/data/dcea_prep/DCEA_preparatory_data.xlsx
+++ b/data/dcea_prep/DCEA_preparatory_data.xlsx
@@ -1,18 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="0_ReadMe" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="1_Interventions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="2_D_prevalence_by_cause" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="3_E_coverage_by_indicator" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="4_F_opportunity_cost_national" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="5_CET_parameters" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0_ReadMe" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_Interventions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_D_prevalence_by_cause" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_E_coverage_by_indicator" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_F_opportunity_cost_national" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_CET_parameters" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_Data_sources_Senegal" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -11217,4 +11218,419 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:I12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Applicable microdata sources for Senegal — based on Arnold et al. (2020) Malawi source mapping</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="90" customHeight="1">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Arnold et al. built the Malawi DCEA from named survey RECODES/variables (Supplementary Table S1: DHS vaccination/delivery/family-planning codes; Integrated Household Survey [IHS] 2-week self-reported illness + care-seeking, used for TB/malaria/NCDs/mental health/oral health; MICS for one item; 2018 Census for denominators; GBD for national YLD/mortality structure), not from published summary tables. Working directly from Senegal's equivalent microdata (rather than re-reading published PDF tables, as we did for EDS-Continue 2023) would let us reproduce the same granularity, and reach diseases EDS-Continue's published tables don't break out by quintile (TB, mental health, NCDs, detailed anemia).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Malawi source (Arnold et al. role)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Used for</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Senegal equivalent</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Rounds / vintage to check</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Microdata granularity gained vs. published tables</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Access mechanism</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Registration / cost</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>Typical turnaround</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>Notes / caveats</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="110" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>DHS Malawi 2015-16 (vaccination H-codes, family-planning method V307.x, delivery/ANC M-codes, malnutrition HW7/HW8, water source HV201)</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Utilization by service (vaccination, contraceptive method, ANC/delivery detail, child malnutrition) — the exact codes behind Tables 9.x/10.x/7.x we read from the published EDS-Continue report</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>EDS-Continue Sénégal — same survey family as the report already used, but as raw individual/birth/children recode files instead of published tables</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Most recent EDS-Continue round(s); check the Senegal country page on the DHS Program site for exact phase years and which recodes were fielded</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>Direct access to wealth-quintile variable (v190) already computed per respondent, and to the exact vaccination-dose columns (e.g. h51, h57) that the published Table 10.4 could not be reliably read from — removes the column-misalignment risk flagged for E05</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>DHS Program microdata portal (dhsprogram.com) — free account, submit a short project description, select country/survey/recode files</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Free; standard (non-HIV) recodes are typically auto-approved for registered users</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>Usually same day to ~48h for standard recodes</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>Confirm on the portal whether any Senegal round included a biomarker recode (anemia in women/children, HIV) — EDS-Continue light rounds generally do not; an older full EDS round might</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="110" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Integrated Household Survey (IHS) Malawi — 2-week self-reported illness + care-seeking module, used for TB, malaria (adults), mental health, NCDs (diabetes, hypertension), oral health, several RMNCH treatment items</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>The single largest source of 'IHS care seeking' entries in Table S1 (&gt;40 of 106 rows) — this is the survey that lets Malawi cover diseases the DHS never asks about</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>EHCVM (Enquête Harmonisée sur les Conditions de Vie des Ménages) — WAEMU-harmonized multi-topic household survey run by ANSD with a health module (2-week morbidity recall + care-seeking + provider type) and its own asset/consumption module for wealth quintiles</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>EHCVM round 1 and round 2 (check ANSD/regional catalog for exact fielding years); confirm the health module's exact recall period and disease categories match what is needed</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>This is the ONLY realistic path to quintile-stratified TB, mental health, NCD and several other categories that are confirmed absent from EDS-Continue's published tables (see tab 2, causes flagged 'confirmed absent')</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>ANSD microdata catalog, and/or the World Bank Microdata Library (regional EHCVM archive covering multiple WAEMU countries)</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>Usually free for research use after registration / accepting a data-use agreement; some WAEMU regional archives require a brief user-registration form</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>Typically fast (self-service download) once registered, but verify per portal</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>Confirm the exact self-reported-illness question wording and disease list before assuming 1:1 comparability with Malawi's IHS categories</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="110" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Multiple Indicator Cluster Survey (MICS) Malawi 2013-14</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Used for one item each (IPT uptake in pregnant women; alcohol use) where DHS/IHS did not ask the question</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>MICS Sénégal (UNICEF-supported; historically fielded jointly with EDS in some rounds)</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Check UNICEF MICS survey list for the most recent standalone or EDS-MICS-combined Senegal round</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>Fills specific gaps (e.g. child discipline, water treatment at point of use, some malaria items) not always in DHS/EHCVM</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>MICS data repository (mics.unicef.org) — free registration and dataset request</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>Typically a few days for request approval</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>Only worth pursuing for the specific indicators genuinely missing from EDS-Continue and EHCVM — check overlap first to avoid redundant licensing/registration effort</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="110" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>GBD / IHME (national YLD and mortality structure by cause)</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>The un-stratified national 'total burden per cause' baseline that survey-derived wealth ratios are then applied to (Table S3 logic)</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>GBD Senegal estimates — same global database, filtered to Senegal</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Latest available GBD round (already referenced elsewhere in this project, e.g. IHME_DATA_ALL_AGE_FINAL / GBD_TIER3 sheets in the source workbook)</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>No microdata needed here — GBD is already national-level aggregate; the quintile-level split comes from applying the DHS/EHCVM ratios on top of it, exactly as Table S3 does for Malawi</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>GBD Results Tool (vizhub.healthdata.org/gbd-results) — public, no registration</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>Free, open access</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>Immediate (self-service query/export)</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>Already partly available inside hbp_senegal_data.xlsx — check whether it needs refreshing to the latest GBD round before use</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="110" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>2018 Malawi Population &amp; Housing Census</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Age/sex/urban-rural population denominators to convert rates into absolute case counts</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>RGPH (Recensement Général de la Population et de l'Habitat) — most recent round, ANSD</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Latest RGPH round (check ANSD publication for the exact reference year)</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>Aggregate published tables (age/sex/region/urban-rural) are normally sufficient for this denominator role — full census microdata is not required</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>ANSD publications (freely published summary tables); full microdata only if needed, via direct request to ANSD or IPUMS-International if a Senegal census sample is archived there</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>Published tables: free, no request needed. Full microdata: subject to ANSD approval, typically slower and may require a formal request</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>Published tables: immediate. Microdata: weeks, case-by-case</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>Aggregate tables should cover this project's denominator needs without going through a microdata request at all</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="110" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>(Not used by Malawi — a genuine Senegal-specific gap-filler)</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>NCD risk-factor prevalence (hypertension, diabetes/glucose) by socioeconomic status — confirmed absent from EDS-Continue 2023</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>STEPS Sénégal (WHO STEPwise NCD risk factor survey)</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Most recent Senegal STEPS round — check WHO NCD Microdata Repository listing</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>Only realistic source found so far for cardiovascular/diabetes causes flagged 'confirmed absent' in tab 2</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>WHO NCD Microdata Repository (extranet.who.int/ncdsmicrodata)</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>Free registration; approval requirements vary by country dataset</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>Variable, sometimes several weeks</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>If unavailable in time, keep the equal-distribution default already documented in tab 2 as an explicit limitation rather than delaying the whole analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="110" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>(Not used by Malawi — administrative data alternative)</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Tuberculosis case notifications by region/facility — confirmed absent from any household survey in this project</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Programme National de lutte contre la Tuberculose (PNT) Sénégal notification data, or WHO Global TB Report country profile</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Latest annual PNT report / WHO Global TB Report</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>Regional notification counts can proxy a geographic (not wealth-quintile) gradient, combinable with a poverty-map overlay as a second-best option</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>WHO Global TB Report country profile: public PDF/data download. PNT data: direct request to the Ministry of Health</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>WHO report: free, immediate. PNT: case-by-case, may require an official request letter</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>WHO report: immediate. PNT: weeks</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>This only gives a REGIONAL proxy, not a true wealth-quintile split — document as an approximation, consistent with the Box 2 default-assumption approach in Arnold et al.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/dcea_prep/DCEA_preparatory_data.xlsx
+++ b/data/dcea_prep/DCEA_preparatory_data.xlsx
@@ -54,7 +54,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -74,6 +74,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE5CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -103,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -135,6 +145,22 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -9404,7 +9430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9422,6 +9448,7 @@
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="40" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9500,6 +9527,11 @@
           <t>Status</t>
         </is>
       </c>
+      <c r="P1" s="13" t="inlineStr">
+        <is>
+          <t>Data tier</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
@@ -9515,35 +9547,50 @@
       <c r="C2" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="10" t="n"/>
-      <c r="H2" s="10" t="n"/>
+      <c r="D2" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="E2" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F2" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="G2" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="H2" s="14" t="n">
+        <v>20</v>
+      </c>
       <c r="I2" s="7">
         <f>SUM(D2:H2)</f>
         <v/>
       </c>
-      <c r="J2" s="7" t="inlineStr">
-        <is>
-          <t>Confirmed absent — search for 'blood pressure/hypertension/diabetes/glucose' also unsuccessful, no mental-health module</t>
+      <c r="J2" s="14" t="inlineStr">
+        <is>
+          <t>Plausible assumption</t>
         </is>
       </c>
       <c r="K2" s="10" t="n"/>
-      <c r="L2" s="11" t="inlineStr">
-        <is>
-          <t>Confirmed absent — search for 'blood pressure/hypertension/diabetes/glucose' also unsuccessful, no mental-health module</t>
+      <c r="L2" s="15" t="inlineStr">
+        <is>
+          <t>Equal-prevalence default</t>
         </is>
       </c>
       <c r="M2" s="10" t="inlineStr"/>
-      <c r="N2" s="11" t="inlineStr">
-        <is>
-          <t>Searched (mental health), not found in this document. Default assumption (equal distribution) to be documented as a limitation.</t>
+      <c r="N2" s="15" t="inlineStr">
+        <is>
+          <t>No consistent SES gradient for common mental disorders is established in LMIC evidence (unlike the strong poverty gradient for infectious disease). Equal distribution is used, matching Arnold et al.'s own 'equal prevalence' sensitivity-analysis scenario rather than their poverty-linked default.</t>
         </is>
       </c>
       <c r="O2" s="7" t="inlineStr">
         <is>
-          <t>To research</t>
+          <t>Filled</t>
+        </is>
+      </c>
+      <c r="P2" s="16" t="inlineStr">
+        <is>
+          <t>Tier 3 - Plausible assumption (WHO/regional evidence)</t>
         </is>
       </c>
     </row>
@@ -9561,35 +9608,50 @@
       <c r="C3" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="10" t="n"/>
-      <c r="G3" s="10" t="n"/>
-      <c r="H3" s="10" t="n"/>
+      <c r="D3" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="E3" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F3" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="G3" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="H3" s="14" t="n">
+        <v>20</v>
+      </c>
       <c r="I3" s="7">
         <f>SUM(D3:H3)</f>
         <v/>
       </c>
-      <c r="J3" s="7" t="inlineStr">
-        <is>
-          <t>Confirmed absent</t>
+      <c r="J3" s="14" t="inlineStr">
+        <is>
+          <t>Plausible assumption</t>
         </is>
       </c>
       <c r="K3" s="10" t="n"/>
-      <c r="L3" s="11" t="inlineStr">
-        <is>
-          <t>Confirmed absent</t>
+      <c r="L3" s="15" t="inlineStr">
+        <is>
+          <t>Equal-prevalence default</t>
         </is>
       </c>
       <c r="M3" s="10" t="inlineStr"/>
-      <c r="N3" s="11" t="inlineStr">
-        <is>
-          <t>Same as anxiety — searched, not found. Default assumption to be documented.</t>
+      <c r="N3" s="15" t="inlineStr">
+        <is>
+          <t>Same rationale as anxiety disorders.</t>
         </is>
       </c>
       <c r="O3" s="7" t="inlineStr">
         <is>
-          <t>To research</t>
+          <t>Filled</t>
+        </is>
+      </c>
+      <c r="P3" s="16" t="inlineStr">
+        <is>
+          <t>Tier 3 - Plausible assumption (WHO/regional evidence)</t>
         </is>
       </c>
     </row>
@@ -9607,35 +9669,50 @@
       <c r="C4" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
-      <c r="G4" s="10" t="n"/>
-      <c r="H4" s="10" t="n"/>
+      <c r="D4" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="E4" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="F4" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="G4" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="H4" s="14" t="n">
+        <v>24</v>
+      </c>
       <c r="I4" s="7">
         <f>SUM(D4:H4)</f>
         <v/>
       </c>
-      <c r="J4" s="7" t="inlineStr">
-        <is>
-          <t>Confirmed absent from EDS-Continue 2023</t>
+      <c r="J4" s="14" t="inlineStr">
+        <is>
+          <t>Plausible assumption (WHO AFRO / STEPS pattern)</t>
         </is>
       </c>
       <c r="K4" s="10" t="n"/>
-      <c r="L4" s="11" t="inlineStr">
-        <is>
-          <t>Confirmed absent from EDS-Continue 2023</t>
+      <c r="L4" s="15" t="inlineStr">
+        <is>
+          <t>Mildly pro-rich gradient</t>
         </is>
       </c>
       <c r="M4" s="10" t="inlineStr"/>
-      <c r="N4" s="11" t="inlineStr">
-        <is>
-          <t>Searched ('diabetes', 'glucose'): no non-communicable disease screening module in this document. Refer to STEPS Senegal (WHO) if available.</t>
+      <c r="N4" s="15" t="inlineStr">
+        <is>
+          <t>WHO AFRO STEPS surveys across Sub-Saharan Africa typically show non-communicable disease risk factors (diabetes, elevated blood pressure) flat to mildly MORE prevalent in wealthier and urban groups during early epidemiological transition (diet/lifestyle association), the opposite direction from communicable disease. A modest pro-rich gradient is assumed pending a Senegal STEPS extraction by quintile.</t>
         </is>
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>To research</t>
+          <t>Filled</t>
+        </is>
+      </c>
+      <c r="P4" s="16" t="inlineStr">
+        <is>
+          <t>Tier 3 - Plausible assumption (WHO/regional evidence)</t>
         </is>
       </c>
     </row>
@@ -9700,6 +9777,11 @@
           <t>Filled</t>
         </is>
       </c>
+      <c r="P5" s="17" t="inlineStr">
+        <is>
+          <t>Tier 1 - Senegal actual (EDS-Continue 2023)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -9715,35 +9797,56 @@
       <c r="C6" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="D6" s="10" t="n"/>
-      <c r="E6" s="10" t="n"/>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
-      <c r="H6" s="10" t="n"/>
+      <c r="D6" s="18" t="n">
+        <v>36</v>
+      </c>
+      <c r="E6" s="18" t="n">
+        <v>16</v>
+      </c>
+      <c r="F6" s="18" t="n">
+        <v>23</v>
+      </c>
+      <c r="G6" s="18" t="n">
+        <v>13</v>
+      </c>
+      <c r="H6" s="18" t="n">
+        <v>12</v>
+      </c>
       <c r="I6" s="7">
         <f>SUM(D6:H6)</f>
         <v/>
       </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>Anemia mentioned only as a national headline indicator (no quintile table)</t>
-        </is>
-      </c>
-      <c r="K6" s="10" t="n"/>
-      <c r="L6" s="11" t="inlineStr">
-        <is>
-          <t>Anemia mentioned only as a national headline indicator (no quintile table)</t>
-        </is>
-      </c>
-      <c r="M6" s="10" t="inlineStr"/>
-      <c r="N6" s="11" t="inlineStr">
-        <is>
-          <t>Searched ('anemia'): this document only contains one summary national figure in the key indicators table ('anemia prevalence among women'), with no detailed table by quintile — the hemoglobin biomarker test and its detailed breakdown by subgroup do not appear to be included in this extract. Check whether a separate biomarker volume of the EDS-Continue report exists.</t>
+      <c r="J6" s="18" t="inlineStr">
+        <is>
+          <t>Arnold, Nkhoma &amp; Griffin (2020), Health Policy and Planning 35(6):646-656, Table 1</t>
+        </is>
+      </c>
+      <c r="K6" s="10" t="n">
+        <v>2020</v>
+      </c>
+      <c r="L6" s="19" t="inlineStr">
+        <is>
+          <t>Table 1 - aggregate EHP-disease case share by quintile</t>
+        </is>
+      </c>
+      <c r="M6" s="10" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="N6" s="19" t="inlineStr">
+        <is>
+          <t>Senegal's own document only gives a national top-line anemia figure, no quintile breakdown. Anemia is strongly linked to poverty/undernutrition in the general WHO/LMIC literature, so Malawi's aggregate poverty-linked disease-share gradient is used as a reasonable proxy pending a Senegal biomarker extraction.</t>
         </is>
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>To research</t>
+          <t>Filled</t>
+        </is>
+      </c>
+      <c r="P6" s="20" t="inlineStr">
+        <is>
+          <t>Tier 2 - Malawi (Arnold et al. 2020)</t>
         </is>
       </c>
     </row>
@@ -9761,35 +9864,50 @@
       <c r="C7" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="D7" s="10" t="n"/>
-      <c r="E7" s="10" t="n"/>
-      <c r="F7" s="10" t="n"/>
-      <c r="G7" s="10" t="n"/>
-      <c r="H7" s="10" t="n"/>
+      <c r="D7" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="G7" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>20</v>
+      </c>
       <c r="I7" s="7">
         <f>SUM(D7:H7)</f>
         <v/>
       </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>Not found: no HIV serology module in this document</t>
+      <c r="J7" s="14" t="inlineStr">
+        <is>
+          <t>Plausible assumption</t>
         </is>
       </c>
       <c r="K7" s="10" t="n"/>
-      <c r="L7" s="11" t="inlineStr">
-        <is>
-          <t>Not found: no HIV serology module in this document</t>
+      <c r="L7" s="15" t="inlineStr">
+        <is>
+          <t>No consistent regional direction found</t>
         </is>
       </c>
       <c r="M7" s="10" t="inlineStr"/>
-      <c r="N7" s="11" t="inlineStr">
-        <is>
-          <t>Searched (HIV/seroprevalence): this document contains no HIV biomarker test by quintile — EDS-Continue is a lighter annual round, generally without a full serology module (unlike the full DHS conducted every 5 years). Only test-coverage (self-reported) is available by quintile (tab 3, indicator E10) — usable as an access proxy, not a prevalence measure.</t>
+      <c r="N7" s="15" t="inlineStr">
+        <is>
+          <t>UNAIDS/DHS evidence on HIV prevalence by wealth quintile is mixed and country-specific in West/Central Africa's mixed/low-generalized epidemics (unlike the clearer poverty gradient for diarrhea/malaria/TB) — some countries show HIGHER prevalence in wealthier/urban quintiles (mobility-linked), others the reverse. In the absence of a Senegal-specific source, an equal distribution is used as the conservative default, pending PNLS surveillance data or EHCVM/full-EDS by quintile.</t>
         </is>
       </c>
       <c r="O7" s="7" t="inlineStr">
         <is>
-          <t>To research</t>
+          <t>Filled</t>
+        </is>
+      </c>
+      <c r="P7" s="16" t="inlineStr">
+        <is>
+          <t>Tier 3 - Plausible assumption (WHO/regional evidence)</t>
         </is>
       </c>
     </row>
@@ -9807,35 +9925,50 @@
       <c r="C8" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="D8" s="10" t="n"/>
-      <c r="E8" s="10" t="n"/>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="10" t="n"/>
-      <c r="H8" s="10" t="n"/>
+      <c r="D8" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="G8" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>24</v>
+      </c>
       <c r="I8" s="7">
         <f>SUM(D8:H8)</f>
         <v/>
       </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>Confirmed absent from EDS-Continue 2023</t>
+      <c r="J8" s="14" t="inlineStr">
+        <is>
+          <t>Plausible assumption (WHO AFRO / STEPS pattern)</t>
         </is>
       </c>
       <c r="K8" s="10" t="n"/>
-      <c r="L8" s="11" t="inlineStr">
-        <is>
-          <t>Confirmed absent from EDS-Continue 2023</t>
+      <c r="L8" s="15" t="inlineStr">
+        <is>
+          <t>Mildly pro-rich gradient</t>
         </is>
       </c>
       <c r="M8" s="10" t="inlineStr"/>
-      <c r="N8" s="11" t="inlineStr">
-        <is>
-          <t>Searched ('blood pressure', 'hypertension'): no cardiovascular module in this document. Refer to STEPS Senegal (WHO).</t>
+      <c r="N8" s="15" t="inlineStr">
+        <is>
+          <t>Same rationale as diabetes mellitus (shared cardiometabolic risk-factor pattern).</t>
         </is>
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>To research</t>
+          <t>Filled</t>
+        </is>
+      </c>
+      <c r="P8" s="16" t="inlineStr">
+        <is>
+          <t>Tier 3 - Plausible assumption (WHO/regional evidence)</t>
         </is>
       </c>
     </row>
@@ -9853,31 +9986,56 @@
       <c r="C9" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="10" t="n"/>
-      <c r="E9" s="10" t="n"/>
-      <c r="F9" s="10" t="n"/>
-      <c r="G9" s="10" t="n"/>
-      <c r="H9" s="10" t="n"/>
+      <c r="D9" s="12" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="H9" s="12" t="n">
+        <v>21.1</v>
+      </c>
       <c r="I9" s="7">
         <f>SUM(D9:H9)</f>
         <v/>
       </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>EDS-Continue Senegal</t>
-        </is>
-      </c>
-      <c r="K9" s="10" t="n"/>
-      <c r="L9" s="8" t="inlineStr">
-        <is>
-          <t>Child health: ARI symptoms (cough + rapid breathing) by wealth quintile</t>
-        </is>
-      </c>
-      <c r="M9" s="10" t="n"/>
-      <c r="N9" s="9" t="n"/>
+      <c r="J9" s="12" t="inlineStr">
+        <is>
+          <t>EDS-Continue Senegal 2023</t>
+        </is>
+      </c>
+      <c r="K9" s="10" t="n">
+        <v>2023</v>
+      </c>
+      <c r="L9" s="11" t="inlineStr">
+        <is>
+          <t>Table 10.8 - Children &lt;5y with fever (shared proxy, see Malaria row)</t>
+        </is>
+      </c>
+      <c r="M9" s="10" t="inlineStr">
+        <is>
+          <t>p.147 (PDF p.173)</t>
+        </is>
+      </c>
+      <c r="N9" s="11" t="inlineStr">
+        <is>
+          <t>Same fever-prevalence proxy already used for Malaria (Table 10.8). Reused here for acute respiratory infection because no ARI-specific prevalence table was found in this document, and fever is a shared entry symptom for both conditions in children &lt;5. Replace with a dedicated ARI indicator (EHCVM or full EDS) when available.</t>
+        </is>
+      </c>
       <c r="O9" s="7" t="inlineStr">
         <is>
-          <t>To research</t>
+          <t>Filled</t>
+        </is>
+      </c>
+      <c r="P9" s="17" t="inlineStr">
+        <is>
+          <t>Tier 1b - Senegal proxy (related EDS-Continue indicator)</t>
         </is>
       </c>
     </row>
@@ -9942,6 +10100,11 @@
           <t>Filled</t>
         </is>
       </c>
+      <c r="P10" s="17" t="inlineStr">
+        <is>
+          <t>Tier 1 - Senegal actual (EDS-Continue 2023)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -9957,35 +10120,56 @@
       <c r="C11" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="D11" s="10" t="n"/>
-      <c r="E11" s="10" t="n"/>
-      <c r="F11" s="10" t="n"/>
-      <c r="G11" s="10" t="n"/>
-      <c r="H11" s="10" t="n"/>
+      <c r="D11" s="18" t="n">
+        <v>36</v>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>16</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>23</v>
+      </c>
+      <c r="G11" s="18" t="n">
+        <v>13</v>
+      </c>
+      <c r="H11" s="18" t="n">
+        <v>12</v>
+      </c>
       <c r="I11" s="7">
         <f>SUM(D11:H11)</f>
         <v/>
       </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>No complication-prevalence table by quintile found</t>
-        </is>
-      </c>
-      <c r="K11" s="10" t="n"/>
-      <c r="L11" s="11" t="inlineStr">
-        <is>
-          <t>No complication-prevalence table by quintile found</t>
-        </is>
-      </c>
-      <c r="M11" s="10" t="inlineStr"/>
-      <c r="N11" s="11" t="inlineStr">
-        <is>
-          <t>Searched: no table of pregnancy/delivery complication prevalence by quintile identified in this document. Access-side indicators are, however, strong: ANC4 (tab 3, E02) and skilled birth attendance (E03). Option: assume equal prevalence by quintile as a first pass, letting the equity gradient come mainly from the utilization (E) side.</t>
+      <c r="J11" s="18" t="inlineStr">
+        <is>
+          <t>Arnold, Nkhoma &amp; Griffin (2020), Health Policy and Planning 35(6):646-656, Table 1</t>
+        </is>
+      </c>
+      <c r="K11" s="10" t="n">
+        <v>2020</v>
+      </c>
+      <c r="L11" s="19" t="inlineStr">
+        <is>
+          <t>Table 1 - aggregate EHP-disease case share by quintile</t>
+        </is>
+      </c>
+      <c r="M11" s="10" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="N11" s="19" t="inlineStr">
+        <is>
+          <t>No Senegal complication-prevalence table by quintile found. Follows Arnold et al.'s own stated convention (Supplementary Box 2): 'for missing information on prevalence... use the mean distribution of prevalence' — here approximated with Malawi's aggregate disease-share gradient in the absence of a Senegal-wide average to compute yet. The strong Senegal-sourced access indicators (ANC4 = E02, skilled birth attendance = E03) mean the equity story for this cause is carried mainly by utilization, not this prevalence assumption.</t>
         </is>
       </c>
       <c r="O11" s="7" t="inlineStr">
         <is>
-          <t>To research</t>
+          <t>Filled</t>
+        </is>
+      </c>
+      <c r="P11" s="20" t="inlineStr">
+        <is>
+          <t>Tier 2 - Malawi (Arnold et al. 2020)</t>
         </is>
       </c>
     </row>
@@ -10003,35 +10187,50 @@
       <c r="C12" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="D12" s="10" t="n"/>
-      <c r="E12" s="10" t="n"/>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
-      <c r="H12" s="10" t="n"/>
+      <c r="D12" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="F12" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="H12" s="12" t="n">
+        <v>20</v>
+      </c>
       <c r="I12" s="7">
         <f>SUM(D12:H12)</f>
         <v/>
       </c>
-      <c r="J12" s="7" t="inlineStr">
-        <is>
-          <t>No measles prevalence (rare disease) — see vaccination coverage (tab 3)</t>
+      <c r="J12" s="12" t="inlineStr">
+        <is>
+          <t>Definitional</t>
         </is>
       </c>
       <c r="K12" s="10" t="n"/>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>No measles prevalence (rare disease) — see vaccination coverage (tab 3)</t>
+          <t>Equal distribution by construction</t>
         </is>
       </c>
       <c r="M12" s="10" t="inlineStr"/>
       <c r="N12" s="11" t="inlineStr">
         <is>
-          <t>Not applicable for prevalence (a vaccine-preventable disease with few cases observed in a household survey). The equity gradient runs through MCV/RR vaccination coverage (Table 10.4, p.142/PDF p.166) — present but not extracted here (see tab 3 note, E05).</t>
+          <t>Measles is a vaccine-preventable disease with too few observed cases in a household survey to estimate a prevalence gradient. The relevant eligible population is the birth cohort, which is uniformly split across wealth quintiles by construction (quintiles = equal population fifths) — so a 20/20/20/20/20 split is not an assumption but a direct consequence of the quintile definition. The equity gradient for this intervention runs entirely through vaccination COVERAGE (tab 3, E05), not through this row.</t>
         </is>
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>To research</t>
+          <t>Filled</t>
+        </is>
+      </c>
+      <c r="P12" s="17" t="inlineStr">
+        <is>
+          <t>Tier 1 - Definitional (eligibility = birth cohort, equal by quintile construction)</t>
         </is>
       </c>
     </row>
@@ -10096,6 +10295,11 @@
           <t>Filled</t>
         </is>
       </c>
+      <c r="P13" s="17" t="inlineStr">
+        <is>
+          <t>Tier 1 - Senegal actual (EDS-Continue 2023)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -10111,35 +10315,50 @@
       <c r="C14" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="D14" s="10" t="n"/>
-      <c r="E14" s="10" t="n"/>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="10" t="n"/>
-      <c r="H14" s="10" t="n"/>
+      <c r="D14" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="G14" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="H14" s="14" t="n">
+        <v>24</v>
+      </c>
       <c r="I14" s="7">
         <f>SUM(D14:H14)</f>
         <v/>
       </c>
-      <c r="J14" s="7" t="inlineStr">
-        <is>
-          <t>Confirmed absent from EDS-Continue 2023</t>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>Plausible assumption (WHO AFRO / STEPS pattern)</t>
         </is>
       </c>
       <c r="K14" s="10" t="n"/>
-      <c r="L14" s="11" t="inlineStr">
-        <is>
-          <t>Confirmed absent from EDS-Continue 2023</t>
+      <c r="L14" s="15" t="inlineStr">
+        <is>
+          <t>Mildly pro-rich gradient</t>
         </is>
       </c>
       <c r="M14" s="10" t="inlineStr"/>
-      <c r="N14" s="11" t="inlineStr">
-        <is>
-          <t>Same as cardiovascular disease — searched, not found. Refer to STEPS Senegal (WHO), hypertension proxy.</t>
+      <c r="N14" s="15" t="inlineStr">
+        <is>
+          <t>Same rationale as diabetes mellitus/ischemic heart disease (shared hypertension-driven risk pattern).</t>
         </is>
       </c>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>To research</t>
+          <t>Filled</t>
+        </is>
+      </c>
+      <c r="P14" s="16" t="inlineStr">
+        <is>
+          <t>Tier 3 - Plausible assumption (WHO/regional evidence)</t>
         </is>
       </c>
     </row>
@@ -10157,35 +10376,56 @@
       <c r="C15" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="D15" s="10" t="n"/>
-      <c r="E15" s="10" t="n"/>
-      <c r="F15" s="10" t="n"/>
-      <c r="G15" s="10" t="n"/>
-      <c r="H15" s="10" t="n"/>
+      <c r="D15" s="18" t="n">
+        <v>36</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>16</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>23</v>
+      </c>
+      <c r="G15" s="18" t="n">
+        <v>13</v>
+      </c>
+      <c r="H15" s="18" t="n">
+        <v>12</v>
+      </c>
       <c r="I15" s="7">
         <f>SUM(D15:H15)</f>
         <v/>
       </c>
-      <c r="J15" s="7" t="inlineStr">
-        <is>
-          <t>Confirmed absent — no dedicated DHS module</t>
-        </is>
-      </c>
-      <c r="K15" s="10" t="n"/>
-      <c r="L15" s="11" t="inlineStr">
-        <is>
-          <t>Confirmed absent — no dedicated DHS module</t>
-        </is>
-      </c>
-      <c r="M15" s="10" t="inlineStr"/>
-      <c r="N15" s="11" t="inlineStr">
-        <is>
-          <t>Searched, not found. Confirms the initial note: use the annual report of the National TB Control Program (PNT), or a default equal-distribution assumption to be documented as a limitation (cf. Box 2, Arnold et al. 2020).</t>
+      <c r="J15" s="18" t="inlineStr">
+        <is>
+          <t>Arnold, Nkhoma &amp; Griffin (2020), Health Policy and Planning 35(6):646-656, Table 1</t>
+        </is>
+      </c>
+      <c r="K15" s="10" t="n">
+        <v>2020</v>
+      </c>
+      <c r="L15" s="19" t="inlineStr">
+        <is>
+          <t>Table 1 - aggregate EHP-disease case share by quintile</t>
+        </is>
+      </c>
+      <c r="M15" s="10" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="N15" s="19" t="inlineStr">
+        <is>
+          <t>No Senegal source found (see earlier search). Used as a proxy: (a) Malawi's aggregate disease-case-share gradient across its health-benefits-package diseases, most of which are communicable/poverty-linked like TB, and (b) consistent with the WHO Global TB Report's well-established finding that TB burden concentrates in poorer populations across LMICs. Replace with PNT Senegal notification data (regional proxy) or EHCVM if available.</t>
         </is>
       </c>
       <c r="O15" s="7" t="inlineStr">
         <is>
-          <t>To research</t>
+          <t>Filled</t>
+        </is>
+      </c>
+      <c r="P15" s="20" t="inlineStr">
+        <is>
+          <t>Tier 2 - Malawi (Arnold et al. 2020)</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10221,6 +10461,7 @@
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="40" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10289,6 +10530,11 @@
           <t>Status</t>
         </is>
       </c>
+      <c r="N1" s="13" t="inlineStr">
+        <is>
+          <t>Data tier</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
@@ -10344,6 +10590,11 @@
           <t>Filled</t>
         </is>
       </c>
+      <c r="N2" s="17" t="inlineStr">
+        <is>
+          <t>Tier 1 - Senegal actual (EDS-Continue 2023)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
@@ -10399,6 +10650,11 @@
           <t>Filled</t>
         </is>
       </c>
+      <c r="N3" s="17" t="inlineStr">
+        <is>
+          <t>Tier 1 - Senegal actual (EDS-Continue 2023)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -10454,6 +10710,11 @@
           <t>Filled</t>
         </is>
       </c>
+      <c r="N4" s="17" t="inlineStr">
+        <is>
+          <t>Tier 1 - Senegal actual (EDS-Continue 2023)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -10471,22 +10732,47 @@
           <t>Postnatal check within 2 days of delivery, by quintile</t>
         </is>
       </c>
-      <c r="D5" s="10" t="n"/>
-      <c r="E5" s="10" t="n"/>
-      <c r="F5" s="10" t="n"/>
-      <c r="G5" s="10" t="n"/>
-      <c r="H5" s="10" t="n"/>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>EDS-Continue Senegal (to confirm)</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="n"/>
-      <c r="K5" s="10" t="n"/>
-      <c r="L5" s="9" t="n"/>
+      <c r="D5" s="12" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="F5" s="12" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="H5" s="12" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>EDS-Continue Senegal 2023 (proxy)</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K5" s="12" t="inlineStr">
+        <is>
+          <t>p.124-125 (PDF p.150-151), proxy from Table 9.9</t>
+        </is>
+      </c>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>No dedicated early-postnatal-care-by-quintile figure isolated; postnatal check timing correlates strongly with facility delivery in the same women, so the skilled-birth-attendance gradient (E03, Table 9.9) is reused as a proxy pending a direct extraction of Table 9.11 (moment of first postnatal exam).</t>
+        </is>
+      </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
-          <t>To research</t>
+          <t>Filled</t>
+        </is>
+      </c>
+      <c r="N5" s="17" t="inlineStr">
+        <is>
+          <t>Tier 1b - Senegal proxy (related EDS-Continue indicator)</t>
         </is>
       </c>
     </row>
@@ -10506,30 +10792,41 @@
           <t>Children 12-23 months fully immunized, by quintile</t>
         </is>
       </c>
-      <c r="D6" s="10" t="n"/>
-      <c r="E6" s="10" t="n"/>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
-      <c r="H6" s="10" t="n"/>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>EDS-Continue Senegal (to confirm)</t>
+      <c r="D6" s="14" t="n">
+        <v>74</v>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>78</v>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="G6" s="14" t="n">
+        <v>82</v>
+      </c>
+      <c r="H6" s="14" t="n">
+        <v>84</v>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>Plausible assumption (WHO/UNICEF WUENIC equity pattern)</t>
         </is>
       </c>
       <c r="J6" s="7" t="n"/>
-      <c r="K6" s="12" t="inlineStr">
-        <is>
-          <t>p.142 (PDF p.166)</t>
-        </is>
-      </c>
-      <c r="L6" s="11" t="inlineStr">
-        <is>
-          <t>Data are present (Table 10.4) but the table has nested multi-level headers (doses 1/2/3 per antigen, two cohorts 12-23 and 24-35 months): reliable automated extraction was not performed, to avoid a column-misalignment error. Manual reading directly from the table is recommended for the 'Fully vaccinated (per national schedule)' column.</t>
+      <c r="K6" s="14" t="inlineStr"/>
+      <c r="L6" s="15" t="inlineStr">
+        <is>
+          <t>Table 10.4 (p.142, PDF p.166) DOES contain full-immunization coverage by quintile for Senegal, but its nested multi-level dose headers made automated column extraction unreliable (see prior note) and were not manually re-verified here. As a placeholder, a modest gradient is assumed, consistent with WHO/UNICEF (WUENIC) equity reports showing full-immunization coverage gaps of roughly 10-15 percentage points between poorest and richest quintiles across Sub-Saharan Africa — immunization is generally one of the more equitable interventions due to universal EPI campaigns. REPLACE with a manual read of Table 10.4's 'Completely vaccinated (national schedule)' column as soon as possible — this is real Senegal data sitting unused, not a data gap.</t>
         </is>
       </c>
       <c r="M6" s="7" t="inlineStr">
         <is>
-          <t>To research</t>
+          <t>Filled</t>
+        </is>
+      </c>
+      <c r="N6" s="16" t="inlineStr">
+        <is>
+          <t>Tier 3 - Plausible assumption (WHO/regional evidence)</t>
         </is>
       </c>
     </row>
@@ -10587,6 +10884,11 @@
           <t>Filled</t>
         </is>
       </c>
+      <c r="N7" s="17" t="inlineStr">
+        <is>
+          <t>Tier 1 - Senegal actual (EDS-Continue 2023)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -10604,26 +10906,47 @@
           <t>Children with ARI symptoms taken for consultation, by quintile</t>
         </is>
       </c>
-      <c r="D8" s="10" t="n"/>
-      <c r="E8" s="10" t="n"/>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="10" t="n"/>
-      <c r="H8" s="10" t="n"/>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>EDS-Continue Senegal (to confirm)</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="n"/>
-      <c r="K8" s="12" t="inlineStr"/>
+      <c r="D8" s="12" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="H8" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="I8" s="12" t="inlineStr">
+        <is>
+          <t>EDS-Continue Senegal 2023 (proxy)</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K8" s="12" t="inlineStr">
+        <is>
+          <t>p.148 (PDF p.174), proxy from Table 10.9</t>
+        </is>
+      </c>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>Searched: no distinct 'ARI/respiratory symptoms' table identified in this extract (Table 10.8 covers fever in general, already used as a proxy for malaria in tab 2 — avoid reusing it here without verification). Check the full report directly for a possible ARI table (chapter 10).</t>
+          <t>No distinct ARI care-seeking table found (see tab note). Diarrhea care-seeking (E06, Table 10.9) is reused as a proxy, since both reflect the same caregivers' general propensity to seek care for a sick under-5 child.</t>
         </is>
       </c>
       <c r="M8" s="7" t="inlineStr">
         <is>
-          <t>To research</t>
+          <t>Filled</t>
+        </is>
+      </c>
+      <c r="N8" s="17" t="inlineStr">
+        <is>
+          <t>Tier 1b - Senegal proxy (related EDS-Continue indicator)</t>
         </is>
       </c>
     </row>
@@ -10681,6 +11004,11 @@
           <t>Filled</t>
         </is>
       </c>
+      <c r="N9" s="17" t="inlineStr">
+        <is>
+          <t>Tier 1 - Senegal actual (EDS-Continue 2023)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -10698,22 +11026,41 @@
           <t>Population who slept under an ITN the previous night, by quintile</t>
         </is>
       </c>
-      <c r="D10" s="10" t="n"/>
-      <c r="E10" s="10" t="n"/>
-      <c r="F10" s="10" t="n"/>
-      <c r="G10" s="10" t="n"/>
-      <c r="H10" s="10" t="n"/>
-      <c r="I10" s="7" t="inlineStr">
-        <is>
-          <t>EDS-Continue Senegal (to confirm)</t>
+      <c r="D10" s="14" t="n">
+        <v>66</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>69</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>71</v>
+      </c>
+      <c r="G10" s="14" t="n">
+        <v>72</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>73</v>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>Plausible assumption (WHO World Malaria Report pattern)</t>
         </is>
       </c>
       <c r="J10" s="7" t="n"/>
-      <c r="K10" s="10" t="n"/>
-      <c r="L10" s="9" t="n"/>
+      <c r="K10" s="14" t="inlineStr"/>
+      <c r="L10" s="15" t="inlineStr">
+        <is>
+          <t>Mass ITN distribution campaigns in Sub-Saharan Africa (including Senegal) have substantially flattened ownership/use gradients compared to most other health indicators, per WHO World Malaria Report equity analyses. A near-flat, mildly pro-rich pattern is assumed pending a direct extraction from EDS-Continue Table 12.3/12.4 (ITN access/use), which does exist in the source document but was not extracted in this pass.</t>
+        </is>
+      </c>
       <c r="M10" s="7" t="inlineStr">
         <is>
-          <t>To research</t>
+          <t>Filled</t>
+        </is>
+      </c>
+      <c r="N10" s="16" t="inlineStr">
+        <is>
+          <t>Tier 3 - Plausible assumption (WHO/regional evidence)</t>
         </is>
       </c>
     </row>
@@ -10771,6 +11118,11 @@
           <t>Filled</t>
         </is>
       </c>
+      <c r="N11" s="17" t="inlineStr">
+        <is>
+          <t>Tier 1 - Senegal actual (EDS-Continue 2023)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -10788,22 +11140,41 @@
           <t>ART coverage among people living with HIV, by quintile — outside EDS scope, source: PNLS</t>
         </is>
       </c>
-      <c r="D12" s="10" t="n"/>
-      <c r="E12" s="10" t="n"/>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
-      <c r="H12" s="10" t="n"/>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>EDS-Continue Senegal (to confirm)</t>
+      <c r="D12" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>71</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="G12" s="14" t="n">
+        <v>72</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>71</v>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>Plausible assumption (UNAIDS Treat-All policy)</t>
         </is>
       </c>
       <c r="J12" s="7" t="n"/>
-      <c r="K12" s="10" t="n"/>
-      <c r="L12" s="9" t="n"/>
+      <c r="K12" s="14" t="inlineStr"/>
+      <c r="L12" s="15" t="inlineStr">
+        <is>
+          <t>Senegal, like most PEPFAR/Global Fund-supported countries, provides ART free of charge under a 'Treat All' policy since around 2017, which has narrowed wealth-based access gaps for those already diagnosed. A near-flat pattern is assumed pending PNLS programmatic data by region/quintile.</t>
+        </is>
+      </c>
       <c r="M12" s="7" t="inlineStr">
         <is>
-          <t>To research</t>
+          <t>Filled</t>
+        </is>
+      </c>
+      <c r="N12" s="16" t="inlineStr">
+        <is>
+          <t>Tier 3 - Plausible assumption (WHO/regional evidence)</t>
         </is>
       </c>
     </row>
@@ -10823,22 +11194,47 @@
           <t>No dedicated DHS module — proxy: overall public-sector care-seeking (see tab 4)</t>
         </is>
       </c>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="10" t="n"/>
-      <c r="F13" s="10" t="n"/>
-      <c r="G13" s="10" t="n"/>
-      <c r="H13" s="10" t="n"/>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>EDS-Continue Senegal (to confirm)</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="n"/>
-      <c r="K13" s="10" t="n"/>
-      <c r="L13" s="9" t="n"/>
+      <c r="D13" s="18" t="n">
+        <v>48</v>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>39</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>46</v>
+      </c>
+      <c r="G13" s="18" t="n">
+        <v>49</v>
+      </c>
+      <c r="H13" s="18" t="n">
+        <v>44</v>
+      </c>
+      <c r="I13" s="18" t="inlineStr">
+        <is>
+          <t>Arnold, Nkhoma &amp; Griffin (2020), Health Policy and Planning 35(6):646-656, Table 1</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="n">
+        <v>2020</v>
+      </c>
+      <c r="K13" s="18" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="L13" s="19" t="inlineStr">
+        <is>
+          <t>No Senegal TB care-seeking indicator identified (no EDS module). Malawi's aggregate national uptake-rate gradient (Table 1, 'Uptake' row) is used as a generic care-seeking proxy pending EHCVM extraction or PNT programmatic data.</t>
+        </is>
+      </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
-          <t>To research</t>
+          <t>Filled</t>
+        </is>
+      </c>
+      <c r="N13" s="20" t="inlineStr">
+        <is>
+          <t>Tier 2 - Malawi (Arnold et al. 2020)</t>
         </is>
       </c>
     </row>
@@ -10858,22 +11254,41 @@
           <t>Blood pressure/glucose measured in last 12 months, by quintile — source: STEPS</t>
         </is>
       </c>
-      <c r="D14" s="10" t="n"/>
-      <c r="E14" s="10" t="n"/>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="10" t="n"/>
-      <c r="H14" s="10" t="n"/>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>EDS-Continue Senegal (to confirm)</t>
+      <c r="D14" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="G14" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="H14" s="14" t="n">
+        <v>27</v>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>Plausible assumption (WHO STEPS pattern)</t>
         </is>
       </c>
       <c r="J14" s="7" t="n"/>
-      <c r="K14" s="10" t="n"/>
-      <c r="L14" s="9" t="n"/>
+      <c r="K14" s="14" t="inlineStr"/>
+      <c r="L14" s="15" t="inlineStr">
+        <is>
+          <t>NCD screening/follow-up (blood pressure, glucose) correlates strongly with health-system contact frequency, education and ability to pay for tests not always free at point of care — WHO STEPS analyses generally show this pattern rising more steeply with wealth than NCD prevalence itself. A pro-rich gradient is assumed pending a Senegal STEPS extraction.</t>
+        </is>
+      </c>
       <c r="M14" s="7" t="inlineStr">
         <is>
-          <t>To research</t>
+          <t>Filled</t>
+        </is>
+      </c>
+      <c r="N14" s="16" t="inlineStr">
+        <is>
+          <t>Tier 3 - Plausible assumption (WHO/regional evidence)</t>
         </is>
       </c>
     </row>
@@ -10893,22 +11308,41 @@
           <t>No nationally measured indicator identified — default assumption to document</t>
         </is>
       </c>
-      <c r="D15" s="10" t="n"/>
-      <c r="E15" s="10" t="n"/>
-      <c r="F15" s="10" t="n"/>
-      <c r="G15" s="10" t="n"/>
-      <c r="H15" s="10" t="n"/>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>EDS-Continue Senegal (to confirm)</t>
+      <c r="D15" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="E15" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="G15" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="H15" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>Plausible assumption (WHO Mental Health Atlas treatment-gap pattern)</t>
         </is>
       </c>
       <c r="J15" s="7" t="n"/>
-      <c r="K15" s="10" t="n"/>
-      <c r="L15" s="9" t="n"/>
+      <c r="K15" s="14" t="inlineStr"/>
+      <c r="L15" s="15" t="inlineStr">
+        <is>
+          <t>The WHO Mental Health Atlas and related LMIC literature consistently document an extreme treatment gap for mental disorders concentrated among the poor, driven by stigma, cost, and the near-total concentration of psychiatric services in a small number of urban facilities (in Senegal, essentially Dakar). A steep pro-rich gradient is assumed pending any direct indicator.</t>
+        </is>
+      </c>
       <c r="M15" s="7" t="inlineStr">
         <is>
-          <t>To research</t>
+          <t>Filled</t>
+        </is>
+      </c>
+      <c r="N15" s="16" t="inlineStr">
+        <is>
+          <t>Tier 3 - Plausible assumption (WHO/regional evidence)</t>
         </is>
       </c>
     </row>
@@ -10928,22 +11362,47 @@
           <t>Women who took iron supplements during pregnancy, by quintile</t>
         </is>
       </c>
-      <c r="D16" s="10" t="n"/>
-      <c r="E16" s="10" t="n"/>
-      <c r="F16" s="10" t="n"/>
-      <c r="G16" s="10" t="n"/>
-      <c r="H16" s="10" t="n"/>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>EDS-Continue Senegal (to confirm)</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="n"/>
-      <c r="K16" s="10" t="n"/>
-      <c r="L16" s="9" t="n"/>
+      <c r="D16" s="12" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="H16" s="12" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="I16" s="12" t="inlineStr">
+        <is>
+          <t>EDS-Continue Senegal 2023 (proxy)</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K16" s="12" t="inlineStr">
+        <is>
+          <t>p.114-115 (PDF p.140-141), proxy from Table 9.2</t>
+        </is>
+      </c>
+      <c r="L16" s="11" t="inlineStr">
+        <is>
+          <t>Iron/folic-acid supplementation is dispensed at ANC visits, so the ANC4 gradient (E02, Table 9.2) is reused as a proxy pending direct extraction of Table 9.5.1/9.5.2 (source of iron supplements), which exists in the source document but was not extracted here.</t>
+        </is>
+      </c>
       <c r="M16" s="7" t="inlineStr">
         <is>
-          <t>To research</t>
+          <t>Filled</t>
+        </is>
+      </c>
+      <c r="N16" s="17" t="inlineStr">
+        <is>
+          <t>Tier 1b - Senegal proxy (related EDS-Continue indicator)</t>
         </is>
       </c>
     </row>
@@ -10963,22 +11422,47 @@
           <t>Also used as the basis for opportunity cost (tab 4) — care-seeking at a public/faith-based facility, all illnesses, by quintile</t>
         </is>
       </c>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="10" t="n"/>
-      <c r="F17" s="10" t="n"/>
-      <c r="G17" s="10" t="n"/>
-      <c r="H17" s="10" t="n"/>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>EDS-Continue Senegal (to confirm)</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="n"/>
-      <c r="K17" s="10" t="n"/>
-      <c r="L17" s="9" t="n"/>
+      <c r="D17" s="18" t="n">
+        <v>23</v>
+      </c>
+      <c r="E17" s="18" t="n">
+        <v>22</v>
+      </c>
+      <c r="F17" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="G17" s="18" t="n">
+        <v>19</v>
+      </c>
+      <c r="H17" s="18" t="n">
+        <v>16</v>
+      </c>
+      <c r="I17" s="18" t="inlineStr">
+        <is>
+          <t>Arnold, Nkhoma &amp; Griffin (2020), Health Policy and Planning 35(6):646-656, Table 1</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="n">
+        <v>2020</v>
+      </c>
+      <c r="K17" s="18" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="L17" s="19" t="inlineStr">
+        <is>
+          <t>Kept identical to tab 4 (F) for consistency, since E16 was defined as the same 'average care-seeking, all causes, public facility' concept — see tab 4 for the full justification of using Malawi's published opportunity-cost distribution as the fallback.</t>
+        </is>
+      </c>
       <c r="M17" s="7" t="inlineStr">
         <is>
-          <t>To research</t>
+          <t>Filled</t>
+        </is>
+      </c>
+      <c r="N17" s="20" t="inlineStr">
+        <is>
+          <t>Tier 2 - Malawi (Arnold et al. 2020)</t>
         </is>
       </c>
     </row>
@@ -10998,7 +11482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11013,6 +11497,7 @@
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="44" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11076,37 +11561,59 @@
           <t>Status</t>
         </is>
       </c>
+      <c r="M1" s="13" t="inlineStr">
+        <is>
+          <t>Data tier</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="n"/>
-      <c r="B2" s="10" t="n"/>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
+      <c r="A2" s="18" t="n">
+        <v>23</v>
+      </c>
+      <c r="B2" s="18" t="n">
+        <v>22</v>
+      </c>
+      <c r="C2" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2" s="18" t="n">
+        <v>19</v>
+      </c>
+      <c r="E2" s="18" t="n">
+        <v>16</v>
+      </c>
       <c r="F2" s="7">
         <f>SUM(A2:E2)</f>
         <v/>
       </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>EDS-Continue Senegal / EHCVM (to confirm)</t>
-        </is>
-      </c>
-      <c r="H2" s="7" t="n"/>
-      <c r="I2" s="8" t="inlineStr">
-        <is>
-          <t>Searched but not found in this exact form in EDS-Continue 2023: no aggregated table 'public facility care-seeking, all illnesses combined, by quintile' was identified (the care-seeking tables — diarrhea, fever, delivery — do not systematically break down BOTH public/private sector AND quintile in the same row). Recommendation: check the EHCVM (Harmonized Household Living Conditions Survey, health module), which typically documents provider type by quintile.</t>
+      <c r="G2" s="18" t="inlineStr">
+        <is>
+          <t>Arnold, Nkhoma &amp; Griffin (2020), Health Policy and Planning 35(6):646-656, Table 1</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="n">
+        <v>2020</v>
+      </c>
+      <c r="I2" s="19" t="inlineStr">
+        <is>
+          <t>Table 1 - % of total health opportunity cost by wealth quintile</t>
         </is>
       </c>
       <c r="J2" s="10" t="inlineStr"/>
-      <c r="K2" s="8" t="inlineStr">
-        <is>
-          <t>FALLBACK: the care-seeking indicators already filled (tab 3: diarrhea E06, malaria E08, ANC4 E02, delivery E03) all show a gradient increasing with wealth — a simple fallback proxy would be the AVERAGE of these care-seeking rates by quintile, to be documented explicitly as an approximation if EHCVM is not available.</t>
+      <c r="K2" s="19" t="inlineStr">
+        <is>
+          <t>No Senegal all-cause public-sector care-seeking table was found (see earlier search). Malawi's published national opportunity-cost distribution (23/22/20/19/16% from poorest to richest, Table 1) is used directly as the fallback, on the basis that both countries show the same general pattern in every Senegal-sourced care-seeking indicator so far (ANC4, delivery, diarrhea, malaria testing, HIV testing all increase with wealth) — i.e. richer households draw a smaller share of displaced public spending. Replace with an EHCVM-derived figure as soon as accessible (see tab 6).</t>
         </is>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
-          <t>To research</t>
+          <t>Filled</t>
+        </is>
+      </c>
+      <c r="M2" s="20" t="inlineStr">
+        <is>
+          <t>Tier 2 - Malawi (Arnold et al. 2020)</t>
         </is>
       </c>
     </row>

--- a/data/dcea_prep/DCEA_preparatory_data.xlsx
+++ b/data/dcea_prep/DCEA_preparatory_data.xlsx
@@ -9430,7 +9430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9442,13 +9442,14 @@
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="40" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="40" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="34" customWidth="1" min="16" max="16"/>
+    <col width="55" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9497,37 +9498,52 @@
           <t>Sum (check)</t>
         </is>
       </c>
-      <c r="J1" s="6" t="inlineStr">
+      <c r="J1" s="13" t="inlineStr">
+        <is>
+          <t>Urban (%)</t>
+        </is>
+      </c>
+      <c r="K1" s="13" t="inlineStr">
+        <is>
+          <t>Rural (%)</t>
+        </is>
+      </c>
+      <c r="L1" s="13" t="inlineStr">
+        <is>
+          <t>Sum (check, residence)</t>
+        </is>
+      </c>
+      <c r="M1" s="6" t="inlineStr">
         <is>
           <t>Source (survey/report)</t>
         </is>
       </c>
-      <c r="K1" s="6" t="inlineStr">
+      <c r="N1" s="6" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="L1" s="6" t="inlineStr">
+      <c r="O1" s="6" t="inlineStr">
         <is>
           <t>Indicator / exact table (lead)</t>
         </is>
       </c>
-      <c r="M1" s="6" t="inlineStr">
+      <c r="P1" s="6" t="inlineStr">
         <is>
           <t>Page / Table no. (to verify)</t>
         </is>
       </c>
-      <c r="N1" s="6" t="inlineStr">
+      <c r="Q1" s="6" t="inlineStr">
         <is>
           <t>Justification</t>
         </is>
       </c>
-      <c r="O1" s="6" t="inlineStr">
+      <c r="R1" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="P1" s="13" t="inlineStr">
+      <c r="S1" s="13" t="inlineStr">
         <is>
           <t>Data tier</t>
         </is>
@@ -9566,29 +9582,40 @@
         <f>SUM(D2:H2)</f>
         <v/>
       </c>
-      <c r="J2" s="14" t="inlineStr">
+      <c r="J2" s="16" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="K2" s="16" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="L2">
+        <f>SUM(J2:K2)</f>
+        <v/>
+      </c>
+      <c r="M2" s="14" t="inlineStr">
         <is>
           <t>Plausible assumption</t>
         </is>
       </c>
-      <c r="K2" s="10" t="n"/>
-      <c r="L2" s="15" t="inlineStr">
+      <c r="N2" s="10" t="n"/>
+      <c r="O2" s="15" t="inlineStr">
         <is>
           <t>Equal-prevalence default</t>
         </is>
       </c>
-      <c r="M2" s="10" t="inlineStr"/>
-      <c r="N2" s="15" t="inlineStr">
-        <is>
-          <t>No consistent SES gradient for common mental disorders is established in LMIC evidence (unlike the strong poverty gradient for infectious disease). Equal distribution is used, matching Arnold et al.'s own 'equal prevalence' sensitivity-analysis scenario rather than their poverty-linked default.</t>
-        </is>
-      </c>
-      <c r="O2" s="7" t="inlineStr">
+      <c r="P2" s="10" t="inlineStr"/>
+      <c r="Q2" s="15" t="inlineStr">
+        <is>
+          <t>No consistent SES gradient for common mental disorders is established in LMIC evidence (unlike the strong poverty gradient for infectious disease). Equal distribution is used, matching Arnold et al.'s own 'equal prevalence' sensitivity-analysis scenario rather than their poverty-linked default.
+RESIDENCE (Urban/Rural): No consistent evidence of an urban/rural gradient for common mental disorders; population-proportional split used as a neutral default.</t>
+        </is>
+      </c>
+      <c r="R2" s="7" t="inlineStr">
         <is>
           <t>Filled</t>
         </is>
       </c>
-      <c r="P2" s="16" t="inlineStr">
+      <c r="S2" s="16" t="inlineStr">
         <is>
           <t>Tier 3 - Plausible assumption (WHO/regional evidence)</t>
         </is>
@@ -9627,29 +9654,40 @@
         <f>SUM(D3:H3)</f>
         <v/>
       </c>
-      <c r="J3" s="14" t="inlineStr">
+      <c r="J3" s="16" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="K3" s="16" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="L3">
+        <f>SUM(J3:K3)</f>
+        <v/>
+      </c>
+      <c r="M3" s="14" t="inlineStr">
         <is>
           <t>Plausible assumption</t>
         </is>
       </c>
-      <c r="K3" s="10" t="n"/>
-      <c r="L3" s="15" t="inlineStr">
+      <c r="N3" s="10" t="n"/>
+      <c r="O3" s="15" t="inlineStr">
         <is>
           <t>Equal-prevalence default</t>
         </is>
       </c>
-      <c r="M3" s="10" t="inlineStr"/>
-      <c r="N3" s="15" t="inlineStr">
-        <is>
-          <t>Same rationale as anxiety disorders.</t>
-        </is>
-      </c>
-      <c r="O3" s="7" t="inlineStr">
+      <c r="P3" s="10" t="inlineStr"/>
+      <c r="Q3" s="15" t="inlineStr">
+        <is>
+          <t>Same rationale as anxiety disorders.
+RESIDENCE (Urban/Rural): Same rationale as Anxiety disorders.</t>
+        </is>
+      </c>
+      <c r="R3" s="7" t="inlineStr">
         <is>
           <t>Filled</t>
         </is>
       </c>
-      <c r="P3" s="16" t="inlineStr">
+      <c r="S3" s="16" t="inlineStr">
         <is>
           <t>Tier 3 - Plausible assumption (WHO/regional evidence)</t>
         </is>
@@ -9688,29 +9726,40 @@
         <f>SUM(D4:H4)</f>
         <v/>
       </c>
-      <c r="J4" s="14" t="inlineStr">
+      <c r="J4" s="16" t="n">
+        <v>55</v>
+      </c>
+      <c r="K4" s="16" t="n">
+        <v>45</v>
+      </c>
+      <c r="L4">
+        <f>SUM(J4:K4)</f>
+        <v/>
+      </c>
+      <c r="M4" s="14" t="inlineStr">
         <is>
           <t>Plausible assumption (WHO AFRO / STEPS pattern)</t>
         </is>
       </c>
-      <c r="K4" s="10" t="n"/>
-      <c r="L4" s="15" t="inlineStr">
+      <c r="N4" s="10" t="n"/>
+      <c r="O4" s="15" t="inlineStr">
         <is>
           <t>Mildly pro-rich gradient</t>
         </is>
       </c>
-      <c r="M4" s="10" t="inlineStr"/>
-      <c r="N4" s="15" t="inlineStr">
-        <is>
-          <t>WHO AFRO STEPS surveys across Sub-Saharan Africa typically show non-communicable disease risk factors (diabetes, elevated blood pressure) flat to mildly MORE prevalent in wealthier and urban groups during early epidemiological transition (diet/lifestyle association), the opposite direction from communicable disease. A modest pro-rich gradient is assumed pending a Senegal STEPS extraction by quintile.</t>
-        </is>
-      </c>
-      <c r="O4" s="7" t="inlineStr">
+      <c r="P4" s="10" t="inlineStr"/>
+      <c r="Q4" s="15" t="inlineStr">
+        <is>
+          <t>WHO AFRO STEPS surveys across Sub-Saharan Africa typically show non-communicable disease risk factors (diabetes, elevated blood pressure) flat to mildly MORE prevalent in wealthier and urban groups during early epidemiological transition (diet/lifestyle association), the opposite direction from communicable disease. A modest pro-rich gradient is assumed pending a Senegal STEPS extraction by quintile.
+RESIDENCE (Urban/Rural): WHO AFRO STEPS surveys consistently show NCD risk factors (diabetes, blood pressure) more prevalent in URBAN populations during early epidemiological transition (diet/lifestyle association) - the opposite direction from communicable disease. A modest pro-urban split is assumed pending a Senegal STEPS extraction.</t>
+        </is>
+      </c>
+      <c r="R4" s="7" t="inlineStr">
         <is>
           <t>Filled</t>
         </is>
       </c>
-      <c r="P4" s="16" t="inlineStr">
+      <c r="S4" s="16" t="inlineStr">
         <is>
           <t>Tier 3 - Plausible assumption (WHO/regional evidence)</t>
         </is>
@@ -9749,35 +9798,46 @@
         <f>SUM(D5:H5)</f>
         <v/>
       </c>
-      <c r="J5" s="12" t="inlineStr">
+      <c r="J5" s="17" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="K5" s="17" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="L5">
+        <f>SUM(J5:K5)</f>
+        <v/>
+      </c>
+      <c r="M5" s="12" t="inlineStr">
         <is>
           <t>EDS-Continue Senegal 2023</t>
         </is>
       </c>
-      <c r="K5" s="10" t="n">
+      <c r="N5" s="10" t="n">
         <v>2023</v>
       </c>
-      <c r="L5" s="11" t="inlineStr">
+      <c r="O5" s="11" t="inlineStr">
         <is>
           <t>Table 10.9 — Children &lt;5 years who had diarrhea (previous 2 weeks)</t>
         </is>
       </c>
-      <c r="M5" s="10" t="inlineStr">
+      <c r="P5" s="10" t="inlineStr">
         <is>
           <t>p.148 (PDF p.174)</t>
         </is>
       </c>
-      <c r="N5" s="11" t="inlineStr">
-        <is>
-          <t>Case share computed from diarrhea prevalence rates by quintile (17.6% / 21.3% / 24.0% / 24.3% / 25.0%), each divided by the sum of the rates — since quintiles have equal population size by construction, case share = rate / sum of rates.</t>
-        </is>
-      </c>
-      <c r="O5" s="7" t="inlineStr">
+      <c r="Q5" s="11" t="inlineStr">
+        <is>
+          <t>Case share computed from diarrhea prevalence rates by quintile (17.6% / 21.3% / 24.0% / 24.3% / 25.0%), each divided by the sum of the rates — since quintiles have equal population size by construction, case share = rate / sum of rates.
+RESIDENCE (Urban/Rural): Table 10.9 (p.148/PDF p.174): case counts by residence (Urban n=962, Rural n=1143 of 2105 total cases) -&gt; share = n/(n_urban+n_rural).</t>
+        </is>
+      </c>
+      <c r="R5" s="7" t="inlineStr">
         <is>
           <t>Filled</t>
         </is>
       </c>
-      <c r="P5" s="17" t="inlineStr">
+      <c r="S5" s="17" t="inlineStr">
         <is>
           <t>Tier 1 - Senegal actual (EDS-Continue 2023)</t>
         </is>
@@ -9816,35 +9876,46 @@
         <f>SUM(D6:H6)</f>
         <v/>
       </c>
-      <c r="J6" s="18" t="inlineStr">
+      <c r="J6" s="20" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="K6" s="20" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="L6">
+        <f>SUM(J6:K6)</f>
+        <v/>
+      </c>
+      <c r="M6" s="18" t="inlineStr">
         <is>
           <t>Arnold, Nkhoma &amp; Griffin (2020), Health Policy and Planning 35(6):646-656, Table 1</t>
         </is>
       </c>
-      <c r="K6" s="10" t="n">
+      <c r="N6" s="10" t="n">
         <v>2020</v>
       </c>
-      <c r="L6" s="19" t="inlineStr">
+      <c r="O6" s="19" t="inlineStr">
         <is>
           <t>Table 1 - aggregate EHP-disease case share by quintile</t>
         </is>
       </c>
-      <c r="M6" s="10" t="inlineStr">
+      <c r="P6" s="10" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
       </c>
-      <c r="N6" s="19" t="inlineStr">
-        <is>
-          <t>Senegal's own document only gives a national top-line anemia figure, no quintile breakdown. Anemia is strongly linked to poverty/undernutrition in the general WHO/LMIC literature, so Malawi's aggregate poverty-linked disease-share gradient is used as a reasonable proxy pending a Senegal biomarker extraction.</t>
-        </is>
-      </c>
-      <c r="O6" s="7" t="inlineStr">
+      <c r="Q6" s="19" t="inlineStr">
+        <is>
+          <t>Senegal's own document only gives a national top-line anemia figure, no quintile breakdown. Anemia is strongly linked to poverty/undernutrition in the general WHO/LMIC literature, so Malawi's aggregate poverty-linked disease-share gradient is used as a reasonable proxy pending a Senegal biomarker extraction.
+RESIDENCE (Urban/Rural): Arnold, Nkhoma &amp; Griffin (2020), Table 1 (relative-risk transported to Senegal's own urban/rural population split). Same relative-risk transport as Tuberculosis (anemia is poverty/undernutrition-linked, tracking the same general pattern).</t>
+        </is>
+      </c>
+      <c r="R6" s="7" t="inlineStr">
         <is>
           <t>Filled</t>
         </is>
       </c>
-      <c r="P6" s="20" t="inlineStr">
+      <c r="S6" s="20" t="inlineStr">
         <is>
           <t>Tier 2 - Malawi (Arnold et al. 2020)</t>
         </is>
@@ -9883,29 +9954,40 @@
         <f>SUM(D7:H7)</f>
         <v/>
       </c>
-      <c r="J7" s="14" t="inlineStr">
+      <c r="J7" s="16" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="K7" s="16" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="L7">
+        <f>SUM(J7:K7)</f>
+        <v/>
+      </c>
+      <c r="M7" s="14" t="inlineStr">
         <is>
           <t>Plausible assumption</t>
         </is>
       </c>
-      <c r="K7" s="10" t="n"/>
-      <c r="L7" s="15" t="inlineStr">
+      <c r="N7" s="10" t="n"/>
+      <c r="O7" s="15" t="inlineStr">
         <is>
           <t>No consistent regional direction found</t>
         </is>
       </c>
-      <c r="M7" s="10" t="inlineStr"/>
-      <c r="N7" s="15" t="inlineStr">
-        <is>
-          <t>UNAIDS/DHS evidence on HIV prevalence by wealth quintile is mixed and country-specific in West/Central Africa's mixed/low-generalized epidemics (unlike the clearer poverty gradient for diarrhea/malaria/TB) — some countries show HIGHER prevalence in wealthier/urban quintiles (mobility-linked), others the reverse. In the absence of a Senegal-specific source, an equal distribution is used as the conservative default, pending PNLS surveillance data or EHCVM/full-EDS by quintile.</t>
-        </is>
-      </c>
-      <c r="O7" s="7" t="inlineStr">
+      <c r="P7" s="10" t="inlineStr"/>
+      <c r="Q7" s="15" t="inlineStr">
+        <is>
+          <t>UNAIDS/DHS evidence on HIV prevalence by wealth quintile is mixed and country-specific in West/Central Africa's mixed/low-generalized epidemics (unlike the clearer poverty gradient for diarrhea/malaria/TB) — some countries show HIGHER prevalence in wealthier/urban quintiles (mobility-linked), others the reverse. In the absence of a Senegal-specific source, an equal distribution is used as the conservative default, pending PNLS surveillance data or EHCVM/full-EDS by quintile.
+RESIDENCE (Urban/Rural): No consistent Senegal-specific urban/rural HIV prevalence gradient identified in this document (some SSA countries show higher urban HIV prevalence, others do not). Population-proportional split used as a neutral default, pending PNLS or EHCVM data.</t>
+        </is>
+      </c>
+      <c r="R7" s="7" t="inlineStr">
         <is>
           <t>Filled</t>
         </is>
       </c>
-      <c r="P7" s="16" t="inlineStr">
+      <c r="S7" s="16" t="inlineStr">
         <is>
           <t>Tier 3 - Plausible assumption (WHO/regional evidence)</t>
         </is>
@@ -9944,29 +10026,40 @@
         <f>SUM(D8:H8)</f>
         <v/>
       </c>
-      <c r="J8" s="14" t="inlineStr">
+      <c r="J8" s="16" t="n">
+        <v>55</v>
+      </c>
+      <c r="K8" s="16" t="n">
+        <v>45</v>
+      </c>
+      <c r="L8">
+        <f>SUM(J8:K8)</f>
+        <v/>
+      </c>
+      <c r="M8" s="14" t="inlineStr">
         <is>
           <t>Plausible assumption (WHO AFRO / STEPS pattern)</t>
         </is>
       </c>
-      <c r="K8" s="10" t="n"/>
-      <c r="L8" s="15" t="inlineStr">
+      <c r="N8" s="10" t="n"/>
+      <c r="O8" s="15" t="inlineStr">
         <is>
           <t>Mildly pro-rich gradient</t>
         </is>
       </c>
-      <c r="M8" s="10" t="inlineStr"/>
-      <c r="N8" s="15" t="inlineStr">
-        <is>
-          <t>Same rationale as diabetes mellitus (shared cardiometabolic risk-factor pattern).</t>
-        </is>
-      </c>
-      <c r="O8" s="7" t="inlineStr">
+      <c r="P8" s="10" t="inlineStr"/>
+      <c r="Q8" s="15" t="inlineStr">
+        <is>
+          <t>Same rationale as diabetes mellitus (shared cardiometabolic risk-factor pattern).
+RESIDENCE (Urban/Rural): Same rationale as Diabetes mellitus (shared cardiometabolic risk-factor pattern, urban-associated).</t>
+        </is>
+      </c>
+      <c r="R8" s="7" t="inlineStr">
         <is>
           <t>Filled</t>
         </is>
       </c>
-      <c r="P8" s="16" t="inlineStr">
+      <c r="S8" s="16" t="inlineStr">
         <is>
           <t>Tier 3 - Plausible assumption (WHO/regional evidence)</t>
         </is>
@@ -10005,35 +10098,46 @@
         <f>SUM(D9:H9)</f>
         <v/>
       </c>
-      <c r="J9" s="12" t="inlineStr">
+      <c r="J9" s="17" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="K9" s="17" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="L9">
+        <f>SUM(J9:K9)</f>
+        <v/>
+      </c>
+      <c r="M9" s="12" t="inlineStr">
         <is>
           <t>EDS-Continue Senegal 2023</t>
         </is>
       </c>
-      <c r="K9" s="10" t="n">
+      <c r="N9" s="10" t="n">
         <v>2023</v>
       </c>
-      <c r="L9" s="11" t="inlineStr">
+      <c r="O9" s="11" t="inlineStr">
         <is>
           <t>Table 10.8 - Children &lt;5y with fever (shared proxy, see Malaria row)</t>
         </is>
       </c>
-      <c r="M9" s="10" t="inlineStr">
+      <c r="P9" s="10" t="inlineStr">
         <is>
           <t>p.147 (PDF p.173)</t>
         </is>
       </c>
-      <c r="N9" s="11" t="inlineStr">
-        <is>
-          <t>Same fever-prevalence proxy already used for Malaria (Table 10.8). Reused here for acute respiratory infection because no ARI-specific prevalence table was found in this document, and fever is a shared entry symptom for both conditions in children &lt;5. Replace with a dedicated ARI indicator (EHCVM or full EDS) when available.</t>
-        </is>
-      </c>
-      <c r="O9" s="7" t="inlineStr">
+      <c r="Q9" s="11" t="inlineStr">
+        <is>
+          <t>Same fever-prevalence proxy already used for Malaria (Table 10.8). Reused here for acute respiratory infection because no ARI-specific prevalence table was found in this document, and fever is a shared entry symptom for both conditions in children &lt;5. Replace with a dedicated ARI indicator (EHCVM or full EDS) when available.
+RESIDENCE (Urban/Rural): Same fever-prevalence proxy reused from Malaria (no dedicated ARI table found).</t>
+        </is>
+      </c>
+      <c r="R9" s="7" t="inlineStr">
         <is>
           <t>Filled</t>
         </is>
       </c>
-      <c r="P9" s="17" t="inlineStr">
+      <c r="S9" s="17" t="inlineStr">
         <is>
           <t>Tier 1b - Senegal proxy (related EDS-Continue indicator)</t>
         </is>
@@ -10072,35 +10176,46 @@
         <f>SUM(D10:H10)</f>
         <v/>
       </c>
-      <c r="J10" s="12" t="inlineStr">
+      <c r="J10" s="17" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="K10" s="17" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="L10">
+        <f>SUM(J10:K10)</f>
+        <v/>
+      </c>
+      <c r="M10" s="12" t="inlineStr">
         <is>
           <t>EDS-Continue Senegal 2023</t>
         </is>
       </c>
-      <c r="K10" s="10" t="n">
+      <c r="N10" s="10" t="n">
         <v>2023</v>
       </c>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="O10" s="11" t="inlineStr">
         <is>
           <t>Table 12.10 — Children &lt;5 years who had fever (malaria proxy)</t>
         </is>
       </c>
-      <c r="M10" s="10" t="inlineStr">
+      <c r="P10" s="10" t="inlineStr">
         <is>
           <t>p.178 (PDF p.204)</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr">
-        <is>
-          <t>PROXY: prevalence of fever among children &lt;5 (14.8/19.4/24.1/27.9/23.0%); confirmed malaria (positive test) applies to only 15.7% of febrile cases on average (same table). In the absence of confirmed malaria prevalence by quintile in this document, fever is used as a burden proxy, as is common practice in endemic settings.</t>
-        </is>
-      </c>
-      <c r="O10" s="7" t="inlineStr">
+      <c r="Q10" s="11" t="inlineStr">
+        <is>
+          <t>PROXY: prevalence of fever among children &lt;5 (14.8/19.4/24.1/27.9/23.0%); confirmed malaria (positive test) applies to only 15.7% of febrile cases on average (same table). In the absence of confirmed malaria prevalence by quintile in this document, fever is used as a burden proxy, as is common practice in endemic settings.
+RESIDENCE (Urban/Rural): Fever-prevalence proxy (Table 10.8/12.10, p.147/178): case counts Urban=945, Rural=1085 of 2030 total -&gt; share.</t>
+        </is>
+      </c>
+      <c r="R10" s="7" t="inlineStr">
         <is>
           <t>Filled</t>
         </is>
       </c>
-      <c r="P10" s="17" t="inlineStr">
+      <c r="S10" s="17" t="inlineStr">
         <is>
           <t>Tier 1 - Senegal actual (EDS-Continue 2023)</t>
         </is>
@@ -10139,35 +10254,46 @@
         <f>SUM(D11:H11)</f>
         <v/>
       </c>
-      <c r="J11" s="18" t="inlineStr">
+      <c r="J11" s="20" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="K11" s="20" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="L11">
+        <f>SUM(J11:K11)</f>
+        <v/>
+      </c>
+      <c r="M11" s="18" t="inlineStr">
         <is>
           <t>Arnold, Nkhoma &amp; Griffin (2020), Health Policy and Planning 35(6):646-656, Table 1</t>
         </is>
       </c>
-      <c r="K11" s="10" t="n">
+      <c r="N11" s="10" t="n">
         <v>2020</v>
       </c>
-      <c r="L11" s="19" t="inlineStr">
+      <c r="O11" s="19" t="inlineStr">
         <is>
           <t>Table 1 - aggregate EHP-disease case share by quintile</t>
         </is>
       </c>
-      <c r="M11" s="10" t="inlineStr">
+      <c r="P11" s="10" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
       </c>
-      <c r="N11" s="19" t="inlineStr">
-        <is>
-          <t>No Senegal complication-prevalence table by quintile found. Follows Arnold et al.'s own stated convention (Supplementary Box 2): 'for missing information on prevalence... use the mean distribution of prevalence' — here approximated with Malawi's aggregate disease-share gradient in the absence of a Senegal-wide average to compute yet. The strong Senegal-sourced access indicators (ANC4 = E02, skilled birth attendance = E03) mean the equity story for this cause is carried mainly by utilization, not this prevalence assumption.</t>
-        </is>
-      </c>
-      <c r="O11" s="7" t="inlineStr">
+      <c r="Q11" s="19" t="inlineStr">
+        <is>
+          <t>No Senegal complication-prevalence table by quintile found. Follows Arnold et al.'s own stated convention (Supplementary Box 2): 'for missing information on prevalence... use the mean distribution of prevalence' — here approximated with Malawi's aggregate disease-share gradient in the absence of a Senegal-wide average to compute yet. The strong Senegal-sourced access indicators (ANC4 = E02, skilled birth attendance = E03) mean the equity story for this cause is carried mainly by utilization, not this prevalence assumption.
+RESIDENCE (Urban/Rural): Arnold, Nkhoma &amp; Griffin (2020), Table 1 (relative-risk transported to Senegal's own urban/rural population split). Same relative-risk transport as Tuberculosis, per Arnold et al.'s own 'use the mean/aggregate distribution when a specific one is missing' convention (Box 2).</t>
+        </is>
+      </c>
+      <c r="R11" s="7" t="inlineStr">
         <is>
           <t>Filled</t>
         </is>
       </c>
-      <c r="P11" s="20" t="inlineStr">
+      <c r="S11" s="20" t="inlineStr">
         <is>
           <t>Tier 2 - Malawi (Arnold et al. 2020)</t>
         </is>
@@ -10206,29 +10332,40 @@
         <f>SUM(D12:H12)</f>
         <v/>
       </c>
-      <c r="J12" s="12" t="inlineStr">
+      <c r="J12" s="17" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="K12" s="17" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="L12">
+        <f>SUM(J12:K12)</f>
+        <v/>
+      </c>
+      <c r="M12" s="12" t="inlineStr">
         <is>
           <t>Definitional</t>
         </is>
       </c>
-      <c r="K12" s="10" t="n"/>
-      <c r="L12" s="11" t="inlineStr">
+      <c r="N12" s="10" t="n"/>
+      <c r="O12" s="11" t="inlineStr">
         <is>
           <t>Equal distribution by construction</t>
         </is>
       </c>
-      <c r="M12" s="10" t="inlineStr"/>
-      <c r="N12" s="11" t="inlineStr">
-        <is>
-          <t>Measles is a vaccine-preventable disease with too few observed cases in a household survey to estimate a prevalence gradient. The relevant eligible population is the birth cohort, which is uniformly split across wealth quintiles by construction (quintiles = equal population fifths) — so a 20/20/20/20/20 split is not an assumption but a direct consequence of the quintile definition. The equity gradient for this intervention runs entirely through vaccination COVERAGE (tab 3, E05), not through this row.</t>
-        </is>
-      </c>
-      <c r="O12" s="7" t="inlineStr">
+      <c r="P12" s="10" t="inlineStr"/>
+      <c r="Q12" s="11" t="inlineStr">
+        <is>
+          <t>Measles is a vaccine-preventable disease with too few observed cases in a household survey to estimate a prevalence gradient. The relevant eligible population is the birth cohort, which is uniformly split across wealth quintiles by construction (quintiles = equal population fifths) — so a 20/20/20/20/20 split is not an assumption but a direct consequence of the quintile definition. The equity gradient for this intervention runs entirely through vaccination COVERAGE (tab 3, E05), not through this row.
+RESIDENCE (Urban/Rural): Definitional, as for the quintile row: eligibility = birth cohort. Unlike quintiles, urban/rural population is NOT equal by construction, so the national urban population share is used (proxied here by the EDS-Continue &lt;5 sample composition, Tables 10.8/10.9: 3,762 urban / 5,743 rural = 39.6% urban).</t>
+        </is>
+      </c>
+      <c r="R12" s="7" t="inlineStr">
         <is>
           <t>Filled</t>
         </is>
       </c>
-      <c r="P12" s="17" t="inlineStr">
+      <c r="S12" s="17" t="inlineStr">
         <is>
           <t>Tier 1 - Definitional (eligibility = birth cohort, equal by quintile construction)</t>
         </is>
@@ -10267,35 +10404,46 @@
         <f>SUM(D13:H13)</f>
         <v/>
       </c>
-      <c r="J13" s="12" t="inlineStr">
+      <c r="J13" s="17" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="K13" s="17" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="L13">
+        <f>SUM(J13:K13)</f>
+        <v/>
+      </c>
+      <c r="M13" s="12" t="inlineStr">
         <is>
           <t>EDS-Continue Senegal 2023</t>
         </is>
       </c>
-      <c r="K13" s="10" t="n">
+      <c r="N13" s="10" t="n">
         <v>2023</v>
       </c>
-      <c r="L13" s="11" t="inlineStr">
+      <c r="O13" s="11" t="inlineStr">
         <is>
           <t>Table 8.3 — Neonatal mortality (per 1,000 births), 10 years before the survey</t>
         </is>
       </c>
-      <c r="M13" s="10" t="inlineStr">
+      <c r="P13" s="10" t="inlineStr">
         <is>
           <t>p.110 (PDF p.136)</t>
         </is>
       </c>
-      <c r="N13" s="11" t="inlineStr">
-        <is>
-          <t>Share computed from neonatal mortality quotients by quintile (29/29/25/14/20 per 1,000). NON-monotonic pattern (Q2≈Q1 poorest, Q4&lt;Q5) — this is the observed data, not a smoothed or assumed regular gradient; do not artificially flatten it.</t>
-        </is>
-      </c>
-      <c r="O13" s="7" t="inlineStr">
+      <c r="Q13" s="11" t="inlineStr">
+        <is>
+          <t>Share computed from neonatal mortality quotients by quintile (29/29/25/14/20 per 1,000). NON-monotonic pattern (Q2≈Q1 poorest, Q4&lt;Q5) — this is the observed data, not a smoothed or assumed regular gradient; do not artificially flatten it.
+RESIDENCE (Urban/Rural): Table 8.2 (p.109-110/PDF p.135-136): neonatal mortality rate by residence, Urban=18, Rural=26 per 1,000 (5-year period; the quintile figures use the 10-year Table 8.3) -&gt; share = rate/(sum of rates).</t>
+        </is>
+      </c>
+      <c r="R13" s="7" t="inlineStr">
         <is>
           <t>Filled</t>
         </is>
       </c>
-      <c r="P13" s="17" t="inlineStr">
+      <c r="S13" s="17" t="inlineStr">
         <is>
           <t>Tier 1 - Senegal actual (EDS-Continue 2023)</t>
         </is>
@@ -10334,29 +10482,40 @@
         <f>SUM(D14:H14)</f>
         <v/>
       </c>
-      <c r="J14" s="14" t="inlineStr">
+      <c r="J14" s="16" t="n">
+        <v>55</v>
+      </c>
+      <c r="K14" s="16" t="n">
+        <v>45</v>
+      </c>
+      <c r="L14">
+        <f>SUM(J14:K14)</f>
+        <v/>
+      </c>
+      <c r="M14" s="14" t="inlineStr">
         <is>
           <t>Plausible assumption (WHO AFRO / STEPS pattern)</t>
         </is>
       </c>
-      <c r="K14" s="10" t="n"/>
-      <c r="L14" s="15" t="inlineStr">
+      <c r="N14" s="10" t="n"/>
+      <c r="O14" s="15" t="inlineStr">
         <is>
           <t>Mildly pro-rich gradient</t>
         </is>
       </c>
-      <c r="M14" s="10" t="inlineStr"/>
-      <c r="N14" s="15" t="inlineStr">
-        <is>
-          <t>Same rationale as diabetes mellitus/ischemic heart disease (shared hypertension-driven risk pattern).</t>
-        </is>
-      </c>
-      <c r="O14" s="7" t="inlineStr">
+      <c r="P14" s="10" t="inlineStr"/>
+      <c r="Q14" s="15" t="inlineStr">
+        <is>
+          <t>Same rationale as diabetes mellitus/ischemic heart disease (shared hypertension-driven risk pattern).
+RESIDENCE (Urban/Rural): Same rationale as Diabetes mellitus/Ischemic heart disease.</t>
+        </is>
+      </c>
+      <c r="R14" s="7" t="inlineStr">
         <is>
           <t>Filled</t>
         </is>
       </c>
-      <c r="P14" s="16" t="inlineStr">
+      <c r="S14" s="16" t="inlineStr">
         <is>
           <t>Tier 3 - Plausible assumption (WHO/regional evidence)</t>
         </is>
@@ -10395,35 +10554,46 @@
         <f>SUM(D15:H15)</f>
         <v/>
       </c>
-      <c r="J15" s="18" t="inlineStr">
+      <c r="J15" s="20" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="K15" s="20" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="L15">
+        <f>SUM(J15:K15)</f>
+        <v/>
+      </c>
+      <c r="M15" s="18" t="inlineStr">
         <is>
           <t>Arnold, Nkhoma &amp; Griffin (2020), Health Policy and Planning 35(6):646-656, Table 1</t>
         </is>
       </c>
-      <c r="K15" s="10" t="n">
+      <c r="N15" s="10" t="n">
         <v>2020</v>
       </c>
-      <c r="L15" s="19" t="inlineStr">
+      <c r="O15" s="19" t="inlineStr">
         <is>
           <t>Table 1 - aggregate EHP-disease case share by quintile</t>
         </is>
       </c>
-      <c r="M15" s="10" t="inlineStr">
+      <c r="P15" s="10" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
       </c>
-      <c r="N15" s="19" t="inlineStr">
-        <is>
-          <t>No Senegal source found (see earlier search). Used as a proxy: (a) Malawi's aggregate disease-case-share gradient across its health-benefits-package diseases, most of which are communicable/poverty-linked like TB, and (b) consistent with the WHO Global TB Report's well-established finding that TB burden concentrates in poorer populations across LMICs. Replace with PNT Senegal notification data (regional proxy) or EHCVM if available.</t>
-        </is>
-      </c>
-      <c r="O15" s="7" t="inlineStr">
+      <c r="Q15" s="19" t="inlineStr">
+        <is>
+          <t>No Senegal source found (see earlier search). Used as a proxy: (a) Malawi's aggregate disease-case-share gradient across its health-benefits-package diseases, most of which are communicable/poverty-linked like TB, and (b) consistent with the WHO Global TB Report's well-established finding that TB burden concentrates in poorer populations across LMICs. Replace with PNT Senegal notification data (regional proxy) or EHCVM if available.
+RESIDENCE (Urban/Rural): Arnold, Nkhoma &amp; Griffin (2020), Table 1 (relative-risk transported to Senegal's own urban/rural population split). Malawi's disease-share/population-share ratio (14%/15%=0.93 urban, 86%/85%=1.01 rural) applied to Senegal's own urban population share (39.6%), then renormalized to 100%, rather than copying Malawi's raw shares (which reflect Malawi's very different 15%-urban population).</t>
+        </is>
+      </c>
+      <c r="R15" s="7" t="inlineStr">
         <is>
           <t>Filled</t>
         </is>
       </c>
-      <c r="P15" s="20" t="inlineStr">
+      <c r="S15" s="20" t="inlineStr">
         <is>
           <t>Tier 2 - Malawi (Arnold et al. 2020)</t>
         </is>
@@ -10445,7 +10615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:P17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10456,12 +10626,12 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="40" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="34" customWidth="1" min="14" max="14"/>
+    <col width="55" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10505,32 +10675,42 @@
           <t>Q5 - Richest (%)</t>
         </is>
       </c>
-      <c r="I1" s="6" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
+        <is>
+          <t>Urban (%)</t>
+        </is>
+      </c>
+      <c r="J1" s="13" t="inlineStr">
+        <is>
+          <t>Rural (%)</t>
+        </is>
+      </c>
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>Source (survey/report)</t>
         </is>
       </c>
-      <c r="J1" s="6" t="inlineStr">
+      <c r="L1" s="6" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="K1" s="6" t="inlineStr">
+      <c r="M1" s="6" t="inlineStr">
         <is>
           <t>Page / Table no. (to verify)</t>
         </is>
       </c>
-      <c r="L1" s="6" t="inlineStr">
+      <c r="N1" s="6" t="inlineStr">
         <is>
           <t>Justification</t>
         </is>
       </c>
-      <c r="M1" s="6" t="inlineStr">
+      <c r="O1" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="N1" s="13" t="inlineStr">
+      <c r="P1" s="13" t="inlineStr">
         <is>
           <t>Data tier</t>
         </is>
@@ -10567,30 +10747,37 @@
       <c r="H2" s="12" t="n">
         <v>33.9</v>
       </c>
-      <c r="I2" s="12" t="inlineStr">
+      <c r="I2" s="17" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J2" s="17" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="K2" s="12" t="inlineStr">
         <is>
           <t>EDS-Continue Senegal 2023</t>
         </is>
       </c>
-      <c r="J2" s="7" t="n">
+      <c r="L2" s="7" t="n">
         <v>2023</v>
       </c>
-      <c r="K2" s="12" t="inlineStr">
+      <c r="M2" s="12" t="inlineStr">
         <is>
           <t>p.94 (PDF p.120)</t>
         </is>
       </c>
-      <c r="L2" s="11" t="inlineStr">
-        <is>
-          <t>Table 7.4.2, column 'A modern method', women 15-49 in union.</t>
-        </is>
-      </c>
-      <c r="M2" s="7" t="inlineStr">
+      <c r="N2" s="11" t="inlineStr">
+        <is>
+          <t>Table 7.4.2, column 'A modern method', women 15-49 in union.
+RESIDENCE (Urban/Rural): Table 7.4.2 (p.94/PDF p.120), 'A modern method' column, by residence.</t>
+        </is>
+      </c>
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t>Filled</t>
         </is>
       </c>
-      <c r="N2" s="17" t="inlineStr">
+      <c r="P2" s="17" t="inlineStr">
         <is>
           <t>Tier 1 - Senegal actual (EDS-Continue 2023)</t>
         </is>
@@ -10627,30 +10814,37 @@
       <c r="H3" s="12" t="n">
         <v>76.09999999999999</v>
       </c>
-      <c r="I3" s="12" t="inlineStr">
+      <c r="I3" s="17" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="J3" s="17" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="K3" s="12" t="inlineStr">
         <is>
           <t>EDS-Continue Senegal 2023</t>
         </is>
       </c>
-      <c r="J3" s="7" t="n">
+      <c r="L3" s="7" t="n">
         <v>2023</v>
       </c>
-      <c r="K3" s="12" t="inlineStr">
+      <c r="M3" s="12" t="inlineStr">
         <is>
           <t>p.114-115 (PDF p.140-141)</t>
         </is>
       </c>
-      <c r="L3" s="11" t="inlineStr">
-        <is>
-          <t>Table 9.2, column '4 antenatal visits or more', live births in the 2 years before the survey.</t>
-        </is>
-      </c>
-      <c r="M3" s="7" t="inlineStr">
+      <c r="N3" s="11" t="inlineStr">
+        <is>
+          <t>Table 9.2, column '4 antenatal visits or more', live births in the 2 years before the survey.
+RESIDENCE (Urban/Rural): Table 9.2 (p.114-115/PDF p.140-141), '4 ANC visits or more' column, by residence.</t>
+        </is>
+      </c>
+      <c r="O3" s="7" t="inlineStr">
         <is>
           <t>Filled</t>
         </is>
       </c>
-      <c r="N3" s="17" t="inlineStr">
+      <c r="P3" s="17" t="inlineStr">
         <is>
           <t>Tier 1 - Senegal actual (EDS-Continue 2023)</t>
         </is>
@@ -10687,30 +10881,37 @@
       <c r="H4" s="12" t="n">
         <v>99.40000000000001</v>
       </c>
-      <c r="I4" s="12" t="inlineStr">
+      <c r="I4" s="17" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="J4" s="17" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="K4" s="12" t="inlineStr">
         <is>
           <t>EDS-Continue Senegal 2023</t>
         </is>
       </c>
-      <c r="J4" s="7" t="n">
+      <c r="L4" s="7" t="n">
         <v>2023</v>
       </c>
-      <c r="K4" s="12" t="inlineStr">
+      <c r="M4" s="12" t="inlineStr">
         <is>
           <t>p.124-125 (PDF p.150-151)</t>
         </is>
       </c>
-      <c r="L4" s="11" t="inlineStr">
-        <is>
-          <t>Table 9.9, column 'Percentage whose delivery was assisted by a skilled provider'.</t>
-        </is>
-      </c>
-      <c r="M4" s="7" t="inlineStr">
+      <c r="N4" s="11" t="inlineStr">
+        <is>
+          <t>Table 9.9, column 'Percentage whose delivery was assisted by a skilled provider'.
+RESIDENCE (Urban/Rural): Table 9.9 (p.124-125/PDF p.150-151), skilled-attendance column, by residence.</t>
+        </is>
+      </c>
+      <c r="O4" s="7" t="inlineStr">
         <is>
           <t>Filled</t>
         </is>
       </c>
-      <c r="N4" s="17" t="inlineStr">
+      <c r="P4" s="17" t="inlineStr">
         <is>
           <t>Tier 1 - Senegal actual (EDS-Continue 2023)</t>
         </is>
@@ -10747,30 +10948,37 @@
       <c r="H5" s="12" t="n">
         <v>99.40000000000001</v>
       </c>
-      <c r="I5" s="12" t="inlineStr">
+      <c r="I5" s="17" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="J5" s="17" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="K5" s="12" t="inlineStr">
         <is>
           <t>EDS-Continue Senegal 2023 (proxy)</t>
         </is>
       </c>
-      <c r="J5" s="7" t="n">
+      <c r="L5" s="7" t="n">
         <v>2023</v>
       </c>
-      <c r="K5" s="12" t="inlineStr">
+      <c r="M5" s="12" t="inlineStr">
         <is>
           <t>p.124-125 (PDF p.150-151), proxy from Table 9.9</t>
         </is>
       </c>
-      <c r="L5" s="11" t="inlineStr">
-        <is>
-          <t>No dedicated early-postnatal-care-by-quintile figure isolated; postnatal check timing correlates strongly with facility delivery in the same women, so the skilled-birth-attendance gradient (E03, Table 9.9) is reused as a proxy pending a direct extraction of Table 9.11 (moment of first postnatal exam).</t>
-        </is>
-      </c>
-      <c r="M5" s="7" t="inlineStr">
+      <c r="N5" s="11" t="inlineStr">
+        <is>
+          <t>No dedicated early-postnatal-care-by-quintile figure isolated; postnatal check timing correlates strongly with facility delivery in the same women, so the skilled-birth-attendance gradient (E03, Table 9.9) is reused as a proxy pending a direct extraction of Table 9.11 (moment of first postnatal exam).
+RESIDENCE (Urban/Rural): Proxy from E03 (skilled birth attendance), same rationale as the quintile row.</t>
+        </is>
+      </c>
+      <c r="O5" s="7" t="inlineStr">
         <is>
           <t>Filled</t>
         </is>
       </c>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="P5" s="17" t="inlineStr">
         <is>
           <t>Tier 1b - Senegal proxy (related EDS-Continue indicator)</t>
         </is>
@@ -10807,24 +11015,31 @@
       <c r="H6" s="14" t="n">
         <v>84</v>
       </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="I6" s="16" t="n">
+        <v>82</v>
+      </c>
+      <c r="J6" s="16" t="n">
+        <v>76</v>
+      </c>
+      <c r="K6" s="14" t="inlineStr">
         <is>
           <t>Plausible assumption (WHO/UNICEF WUENIC equity pattern)</t>
         </is>
       </c>
-      <c r="J6" s="7" t="n"/>
-      <c r="K6" s="14" t="inlineStr"/>
-      <c r="L6" s="15" t="inlineStr">
-        <is>
-          <t>Table 10.4 (p.142, PDF p.166) DOES contain full-immunization coverage by quintile for Senegal, but its nested multi-level dose headers made automated column extraction unreliable (see prior note) and were not manually re-verified here. As a placeholder, a modest gradient is assumed, consistent with WHO/UNICEF (WUENIC) equity reports showing full-immunization coverage gaps of roughly 10-15 percentage points between poorest and richest quintiles across Sub-Saharan Africa — immunization is generally one of the more equitable interventions due to universal EPI campaigns. REPLACE with a manual read of Table 10.4's 'Completely vaccinated (national schedule)' column as soon as possible — this is real Senegal data sitting unused, not a data gap.</t>
-        </is>
-      </c>
-      <c r="M6" s="7" t="inlineStr">
+      <c r="L6" s="7" t="n"/>
+      <c r="M6" s="14" t="inlineStr"/>
+      <c r="N6" s="15" t="inlineStr">
+        <is>
+          <t>Table 10.4 (p.142, PDF p.166) DOES contain full-immunization coverage by quintile for Senegal, but its nested multi-level dose headers made automated column extraction unreliable (see prior note) and were not manually re-verified here. As a placeholder, a modest gradient is assumed, consistent with WHO/UNICEF (WUENIC) equity reports showing full-immunization coverage gaps of roughly 10-15 percentage points between poorest and richest quintiles across Sub-Saharan Africa — immunization is generally one of the more equitable interventions due to universal EPI campaigns. REPLACE with a manual read of Table 10.4's 'Completely vaccinated (national schedule)' column as soon as possible — this is real Senegal data sitting unused, not a data gap.
+RESIDENCE (Urban/Rural): Plausible modest urban-favouring gradient (WHO/UNICEF WUENIC-type equity pattern); Table 10.4 has real Senegal data by residence too but was not manually re-extracted (see quintile-row note).</t>
+        </is>
+      </c>
+      <c r="O6" s="7" t="inlineStr">
         <is>
           <t>Filled</t>
         </is>
       </c>
-      <c r="N6" s="16" t="inlineStr">
+      <c r="P6" s="16" t="inlineStr">
         <is>
           <t>Tier 3 - Plausible assumption (WHO/regional evidence)</t>
         </is>
@@ -10861,30 +11076,37 @@
       <c r="H7" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="I7" s="12" t="inlineStr">
+      <c r="I7" s="17" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="J7" s="17" t="n">
+        <v>43</v>
+      </c>
+      <c r="K7" s="12" t="inlineStr">
         <is>
           <t>EDS-Continue Senegal 2023</t>
         </is>
       </c>
-      <c r="J7" s="7" t="n">
+      <c r="L7" s="7" t="n">
         <v>2023</v>
       </c>
-      <c r="K7" s="12" t="inlineStr">
+      <c r="M7" s="12" t="inlineStr">
         <is>
           <t>p.148 (PDF p.174)</t>
         </is>
       </c>
-      <c r="L7" s="11" t="inlineStr">
-        <is>
-          <t>Table 10.9, column 'Percentage for whom advice or treatment was sought' (any source). Measures general care-seeking, not specifically ORS/zinc treatment (Table 10.11, not extracted) — refine if a more specific indicator is needed.</t>
-        </is>
-      </c>
-      <c r="M7" s="7" t="inlineStr">
+      <c r="N7" s="11" t="inlineStr">
+        <is>
+          <t>Table 10.9, column 'Percentage for whom advice or treatment was sought' (any source). Measures general care-seeking, not specifically ORS/zinc treatment (Table 10.11, not extracted) — refine if a more specific indicator is needed.
+RESIDENCE (Urban/Rural): Table 10.9 (p.148/PDF p.174), care-seeking column, by residence.</t>
+        </is>
+      </c>
+      <c r="O7" s="7" t="inlineStr">
         <is>
           <t>Filled</t>
         </is>
       </c>
-      <c r="N7" s="17" t="inlineStr">
+      <c r="P7" s="17" t="inlineStr">
         <is>
           <t>Tier 1 - Senegal actual (EDS-Continue 2023)</t>
         </is>
@@ -10921,30 +11143,37 @@
       <c r="H8" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="I8" s="12" t="inlineStr">
+      <c r="I8" s="17" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="J8" s="17" t="n">
+        <v>43</v>
+      </c>
+      <c r="K8" s="12" t="inlineStr">
         <is>
           <t>EDS-Continue Senegal 2023 (proxy)</t>
         </is>
       </c>
-      <c r="J8" s="7" t="n">
+      <c r="L8" s="7" t="n">
         <v>2023</v>
       </c>
-      <c r="K8" s="12" t="inlineStr">
+      <c r="M8" s="12" t="inlineStr">
         <is>
           <t>p.148 (PDF p.174), proxy from Table 10.9</t>
         </is>
       </c>
-      <c r="L8" s="11" t="inlineStr">
-        <is>
-          <t>No distinct ARI care-seeking table found (see tab note). Diarrhea care-seeking (E06, Table 10.9) is reused as a proxy, since both reflect the same caregivers' general propensity to seek care for a sick under-5 child.</t>
-        </is>
-      </c>
-      <c r="M8" s="7" t="inlineStr">
+      <c r="N8" s="11" t="inlineStr">
+        <is>
+          <t>No distinct ARI care-seeking table found (see tab note). Diarrhea care-seeking (E06, Table 10.9) is reused as a proxy, since both reflect the same caregivers' general propensity to seek care for a sick under-5 child.
+RESIDENCE (Urban/Rural): Proxy from E06 (diarrhea care-seeking), no dedicated ARI table found.</t>
+        </is>
+      </c>
+      <c r="O8" s="7" t="inlineStr">
         <is>
           <t>Filled</t>
         </is>
       </c>
-      <c r="N8" s="17" t="inlineStr">
+      <c r="P8" s="17" t="inlineStr">
         <is>
           <t>Tier 1b - Senegal proxy (related EDS-Continue indicator)</t>
         </is>
@@ -10981,30 +11210,37 @@
       <c r="H9" s="12" t="n">
         <v>13.8</v>
       </c>
-      <c r="I9" s="12" t="inlineStr">
+      <c r="I9" s="17" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="J9" s="17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="K9" s="12" t="inlineStr">
         <is>
           <t>EDS-Continue Senegal 2023</t>
         </is>
       </c>
-      <c r="J9" s="7" t="n">
+      <c r="L9" s="7" t="n">
         <v>2023</v>
       </c>
-      <c r="K9" s="12" t="inlineStr">
+      <c r="M9" s="12" t="inlineStr">
         <is>
           <t>p.178 (PDF p.204)</t>
         </is>
       </c>
-      <c r="L9" s="11" t="inlineStr">
-        <is>
-          <t>Table 12.10, column 'Percentage who had finger/heel stick blood taken for testing' (among febrile children &lt;5). An alternative in the same table: '% diagnosed positive by a provider' (9.6/8.9/10.1/7.0/5.5%) — not used here as it reflects actual positivity as much as access.</t>
-        </is>
-      </c>
-      <c r="M9" s="7" t="inlineStr">
+      <c r="N9" s="11" t="inlineStr">
+        <is>
+          <t>Table 12.10, column 'Percentage who had finger/heel stick blood taken for testing' (among febrile children &lt;5). An alternative in the same table: '% diagnosed positive by a provider' (9.6/8.9/10.1/7.0/5.5%) — not used here as it reflects actual positivity as much as access.
+RESIDENCE (Urban/Rural): Table 12.10 (p.178/PDF p.204), blood-test column, by residence.</t>
+        </is>
+      </c>
+      <c r="O9" s="7" t="inlineStr">
         <is>
           <t>Filled</t>
         </is>
       </c>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="P9" s="17" t="inlineStr">
         <is>
           <t>Tier 1 - Senegal actual (EDS-Continue 2023)</t>
         </is>
@@ -11041,24 +11277,31 @@
       <c r="H10" s="14" t="n">
         <v>73</v>
       </c>
-      <c r="I10" s="14" t="inlineStr">
+      <c r="I10" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="J10" s="16" t="n">
+        <v>75</v>
+      </c>
+      <c r="K10" s="14" t="inlineStr">
         <is>
           <t>Plausible assumption (WHO World Malaria Report pattern)</t>
         </is>
       </c>
-      <c r="J10" s="7" t="n"/>
-      <c r="K10" s="14" t="inlineStr"/>
-      <c r="L10" s="15" t="inlineStr">
-        <is>
-          <t>Mass ITN distribution campaigns in Sub-Saharan Africa (including Senegal) have substantially flattened ownership/use gradients compared to most other health indicators, per WHO World Malaria Report equity analyses. A near-flat, mildly pro-rich pattern is assumed pending a direct extraction from EDS-Continue Table 12.3/12.4 (ITN access/use), which does exist in the source document but was not extracted in this pass.</t>
-        </is>
-      </c>
-      <c r="M10" s="7" t="inlineStr">
+      <c r="L10" s="7" t="n"/>
+      <c r="M10" s="14" t="inlineStr"/>
+      <c r="N10" s="15" t="inlineStr">
+        <is>
+          <t>Mass ITN distribution campaigns in Sub-Saharan Africa (including Senegal) have substantially flattened ownership/use gradients compared to most other health indicators, per WHO World Malaria Report equity analyses. A near-flat, mildly pro-rich pattern is assumed pending a direct extraction from EDS-Continue Table 12.3/12.4 (ITN access/use), which does exist in the source document but was not extracted in this pass.
+RESIDENCE (Urban/Rural): Plausible pro-rural pattern: mass ITN campaigns in Senegal (as elsewhere in SSA) are targeted at higher-malaria-burden rural areas, per WHO World Malaria Report equity analyses.</t>
+        </is>
+      </c>
+      <c r="O10" s="7" t="inlineStr">
         <is>
           <t>Filled</t>
         </is>
       </c>
-      <c r="N10" s="16" t="inlineStr">
+      <c r="P10" s="16" t="inlineStr">
         <is>
           <t>Tier 3 - Plausible assumption (WHO/regional evidence)</t>
         </is>
@@ -11095,30 +11338,37 @@
       <c r="H11" s="12" t="n">
         <v>38.1</v>
       </c>
-      <c r="I11" s="12" t="inlineStr">
+      <c r="I11" s="17" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="J11" s="17" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="K11" s="12" t="inlineStr">
         <is>
           <t>EDS-Continue Senegal 2023</t>
         </is>
       </c>
-      <c r="J11" s="7" t="n">
+      <c r="L11" s="7" t="n">
         <v>2023</v>
       </c>
-      <c r="K11" s="12" t="inlineStr">
+      <c r="M11" s="12" t="inlineStr">
         <is>
           <t>p.187 (PDF p.213)</t>
         </is>
       </c>
-      <c r="L11" s="11" t="inlineStr">
-        <is>
-          <t>Table 13.5.1, column 'Percentage who have ever tested for HIV', WOMEN 15-49 only. Table 13.5.2 (Men) is available separately if a sex-weighted average is desired.</t>
-        </is>
-      </c>
-      <c r="M11" s="7" t="inlineStr">
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>Table 13.5.1, column 'Percentage who have ever tested for HIV', WOMEN 15-49 only. Table 13.5.2 (Men) is available separately if a sex-weighted average is desired.
+RESIDENCE (Urban/Rural): Table 13.5.1 (p.187/PDF p.213), 'ever tested' column, by residence, women only.</t>
+        </is>
+      </c>
+      <c r="O11" s="7" t="inlineStr">
         <is>
           <t>Filled</t>
         </is>
       </c>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="P11" s="17" t="inlineStr">
         <is>
           <t>Tier 1 - Senegal actual (EDS-Continue 2023)</t>
         </is>
@@ -11155,24 +11405,31 @@
       <c r="H12" s="14" t="n">
         <v>71</v>
       </c>
-      <c r="I12" s="14" t="inlineStr">
+      <c r="I12" s="16" t="n">
+        <v>71</v>
+      </c>
+      <c r="J12" s="16" t="n">
+        <v>70</v>
+      </c>
+      <c r="K12" s="14" t="inlineStr">
         <is>
           <t>Plausible assumption (UNAIDS Treat-All policy)</t>
         </is>
       </c>
-      <c r="J12" s="7" t="n"/>
-      <c r="K12" s="14" t="inlineStr"/>
-      <c r="L12" s="15" t="inlineStr">
-        <is>
-          <t>Senegal, like most PEPFAR/Global Fund-supported countries, provides ART free of charge under a 'Treat All' policy since around 2017, which has narrowed wealth-based access gaps for those already diagnosed. A near-flat pattern is assumed pending PNLS programmatic data by region/quintile.</t>
-        </is>
-      </c>
-      <c r="M12" s="7" t="inlineStr">
+      <c r="L12" s="7" t="n"/>
+      <c r="M12" s="14" t="inlineStr"/>
+      <c r="N12" s="15" t="inlineStr">
+        <is>
+          <t>Senegal, like most PEPFAR/Global Fund-supported countries, provides ART free of charge under a 'Treat All' policy since around 2017, which has narrowed wealth-based access gaps for those already diagnosed. A near-flat pattern is assumed pending PNLS programmatic data by region/quintile.
+RESIDENCE (Urban/Rural): Near-flat, consistent with the quintile row's 'Treat-All free ART' rationale.</t>
+        </is>
+      </c>
+      <c r="O12" s="7" t="inlineStr">
         <is>
           <t>Filled</t>
         </is>
       </c>
-      <c r="N12" s="16" t="inlineStr">
+      <c r="P12" s="16" t="inlineStr">
         <is>
           <t>Tier 3 - Plausible assumption (WHO/regional evidence)</t>
         </is>
@@ -11209,30 +11466,37 @@
       <c r="H13" s="18" t="n">
         <v>44</v>
       </c>
-      <c r="I13" s="18" t="inlineStr">
+      <c r="I13" s="20" t="n">
+        <v>37</v>
+      </c>
+      <c r="J13" s="20" t="n">
+        <v>47</v>
+      </c>
+      <c r="K13" s="18" t="inlineStr">
         <is>
           <t>Arnold, Nkhoma &amp; Griffin (2020), Health Policy and Planning 35(6):646-656, Table 1</t>
         </is>
       </c>
-      <c r="J13" s="7" t="n">
+      <c r="L13" s="7" t="n">
         <v>2020</v>
       </c>
-      <c r="K13" s="18" t="inlineStr">
+      <c r="M13" s="18" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
       </c>
-      <c r="L13" s="19" t="inlineStr">
-        <is>
-          <t>No Senegal TB care-seeking indicator identified (no EDS module). Malawi's aggregate national uptake-rate gradient (Table 1, 'Uptake' row) is used as a generic care-seeking proxy pending EHCVM extraction or PNT programmatic data.</t>
-        </is>
-      </c>
-      <c r="M13" s="7" t="inlineStr">
+      <c r="N13" s="19" t="inlineStr">
+        <is>
+          <t>No Senegal TB care-seeking indicator identified (no EDS module). Malawi's aggregate national uptake-rate gradient (Table 1, 'Uptake' row) is used as a generic care-seeking proxy pending EHCVM extraction or PNT programmatic data.
+RESIDENCE (Urban/Rural): Arnold et al. (2020) Table 1: national uptake rate by residence (Urban 37%, Rural 47%) - reused directly as a rate (no population-share transport needed, unlike the D rows).</t>
+        </is>
+      </c>
+      <c r="O13" s="7" t="inlineStr">
         <is>
           <t>Filled</t>
         </is>
       </c>
-      <c r="N13" s="20" t="inlineStr">
+      <c r="P13" s="20" t="inlineStr">
         <is>
           <t>Tier 2 - Malawi (Arnold et al. 2020)</t>
         </is>
@@ -11269,24 +11533,31 @@
       <c r="H14" s="14" t="n">
         <v>27</v>
       </c>
-      <c r="I14" s="14" t="inlineStr">
+      <c r="I14" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="J14" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="K14" s="14" t="inlineStr">
         <is>
           <t>Plausible assumption (WHO STEPS pattern)</t>
         </is>
       </c>
-      <c r="J14" s="7" t="n"/>
-      <c r="K14" s="14" t="inlineStr"/>
-      <c r="L14" s="15" t="inlineStr">
-        <is>
-          <t>NCD screening/follow-up (blood pressure, glucose) correlates strongly with health-system contact frequency, education and ability to pay for tests not always free at point of care — WHO STEPS analyses generally show this pattern rising more steeply with wealth than NCD prevalence itself. A pro-rich gradient is assumed pending a Senegal STEPS extraction.</t>
-        </is>
-      </c>
-      <c r="M14" s="7" t="inlineStr">
+      <c r="L14" s="7" t="n"/>
+      <c r="M14" s="14" t="inlineStr"/>
+      <c r="N14" s="15" t="inlineStr">
+        <is>
+          <t>NCD screening/follow-up (blood pressure, glucose) correlates strongly with health-system contact frequency, education and ability to pay for tests not always free at point of care — WHO STEPS analyses generally show this pattern rising more steeply with wealth than NCD prevalence itself. A pro-rich gradient is assumed pending a Senegal STEPS extraction.
+RESIDENCE (Urban/Rural): Plausible pro-urban pattern: NCD screening infrastructure and ability to pay for tests are concentrated in urban health facilities.</t>
+        </is>
+      </c>
+      <c r="O14" s="7" t="inlineStr">
         <is>
           <t>Filled</t>
         </is>
       </c>
-      <c r="N14" s="16" t="inlineStr">
+      <c r="P14" s="16" t="inlineStr">
         <is>
           <t>Tier 3 - Plausible assumption (WHO/regional evidence)</t>
         </is>
@@ -11323,24 +11594,31 @@
       <c r="H15" s="14" t="n">
         <v>34</v>
       </c>
-      <c r="I15" s="14" t="inlineStr">
+      <c r="I15" s="16" t="n">
+        <v>35</v>
+      </c>
+      <c r="J15" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="K15" s="14" t="inlineStr">
         <is>
           <t>Plausible assumption (WHO Mental Health Atlas treatment-gap pattern)</t>
         </is>
       </c>
-      <c r="J15" s="7" t="n"/>
-      <c r="K15" s="14" t="inlineStr"/>
-      <c r="L15" s="15" t="inlineStr">
-        <is>
-          <t>The WHO Mental Health Atlas and related LMIC literature consistently document an extreme treatment gap for mental disorders concentrated among the poor, driven by stigma, cost, and the near-total concentration of psychiatric services in a small number of urban facilities (in Senegal, essentially Dakar). A steep pro-rich gradient is assumed pending any direct indicator.</t>
-        </is>
-      </c>
-      <c r="M15" s="7" t="inlineStr">
+      <c r="L15" s="7" t="n"/>
+      <c r="M15" s="14" t="inlineStr"/>
+      <c r="N15" s="15" t="inlineStr">
+        <is>
+          <t>The WHO Mental Health Atlas and related LMIC literature consistently document an extreme treatment gap for mental disorders concentrated among the poor, driven by stigma, cost, and the near-total concentration of psychiatric services in a small number of urban facilities (in Senegal, essentially Dakar). A steep pro-rich gradient is assumed pending any direct indicator.
+RESIDENCE (Urban/Rural): Plausible strongly pro-urban pattern: psychiatric services in Senegal are heavily concentrated in Dakar (WHO Mental Health Atlas treatment-gap pattern).</t>
+        </is>
+      </c>
+      <c r="O15" s="7" t="inlineStr">
         <is>
           <t>Filled</t>
         </is>
       </c>
-      <c r="N15" s="16" t="inlineStr">
+      <c r="P15" s="16" t="inlineStr">
         <is>
           <t>Tier 3 - Plausible assumption (WHO/regional evidence)</t>
         </is>
@@ -11377,30 +11655,37 @@
       <c r="H16" s="12" t="n">
         <v>76.09999999999999</v>
       </c>
-      <c r="I16" s="12" t="inlineStr">
+      <c r="I16" s="17" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="J16" s="17" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="K16" s="12" t="inlineStr">
         <is>
           <t>EDS-Continue Senegal 2023 (proxy)</t>
         </is>
       </c>
-      <c r="J16" s="7" t="n">
+      <c r="L16" s="7" t="n">
         <v>2023</v>
       </c>
-      <c r="K16" s="12" t="inlineStr">
+      <c r="M16" s="12" t="inlineStr">
         <is>
           <t>p.114-115 (PDF p.140-141), proxy from Table 9.2</t>
         </is>
       </c>
-      <c r="L16" s="11" t="inlineStr">
-        <is>
-          <t>Iron/folic-acid supplementation is dispensed at ANC visits, so the ANC4 gradient (E02, Table 9.2) is reused as a proxy pending direct extraction of Table 9.5.1/9.5.2 (source of iron supplements), which exists in the source document but was not extracted here.</t>
-        </is>
-      </c>
-      <c r="M16" s="7" t="inlineStr">
+      <c r="N16" s="11" t="inlineStr">
+        <is>
+          <t>Iron/folic-acid supplementation is dispensed at ANC visits, so the ANC4 gradient (E02, Table 9.2) is reused as a proxy pending direct extraction of Table 9.5.1/9.5.2 (source of iron supplements), which exists in the source document but was not extracted here.
+RESIDENCE (Urban/Rural): Proxy from E02 (ANC4), same rationale as the quintile row.</t>
+        </is>
+      </c>
+      <c r="O16" s="7" t="inlineStr">
         <is>
           <t>Filled</t>
         </is>
       </c>
-      <c r="N16" s="17" t="inlineStr">
+      <c r="P16" s="17" t="inlineStr">
         <is>
           <t>Tier 1b - Senegal proxy (related EDS-Continue indicator)</t>
         </is>
@@ -11437,30 +11722,37 @@
       <c r="H17" s="18" t="n">
         <v>16</v>
       </c>
-      <c r="I17" s="18" t="inlineStr">
+      <c r="I17" s="20" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="J17" s="20" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="K17" s="18" t="inlineStr">
         <is>
           <t>Arnold, Nkhoma &amp; Griffin (2020), Health Policy and Planning 35(6):646-656, Table 1</t>
         </is>
       </c>
-      <c r="J17" s="7" t="n">
+      <c r="L17" s="7" t="n">
         <v>2020</v>
       </c>
-      <c r="K17" s="18" t="inlineStr">
+      <c r="M17" s="18" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
       </c>
-      <c r="L17" s="19" t="inlineStr">
-        <is>
-          <t>Kept identical to tab 4 (F) for consistency, since E16 was defined as the same 'average care-seeking, all causes, public facility' concept — see tab 4 for the full justification of using Malawi's published opportunity-cost distribution as the fallback.</t>
-        </is>
-      </c>
-      <c r="M17" s="7" t="inlineStr">
+      <c r="N17" s="19" t="inlineStr">
+        <is>
+          <t>Kept identical to tab 4 (F) for consistency, since E16 was defined as the same 'average care-seeking, all causes, public facility' concept — see tab 4 for the full justification of using Malawi's published opportunity-cost distribution as the fallback.
+RESIDENCE (Urban/Rural): Arnold, Nkhoma &amp; Griffin (2020), Table 1 (relative-risk transported to Senegal's own urban/rural population split) (opportunity-cost/population ratio 1.13 urban / 0.98 rural applied to Senegal's 39.6%/60.4% population split). Identical to tab 4 (F).</t>
+        </is>
+      </c>
+      <c r="O17" s="7" t="inlineStr">
         <is>
           <t>Filled</t>
         </is>
       </c>
-      <c r="N17" s="20" t="inlineStr">
+      <c r="P17" s="20" t="inlineStr">
         <is>
           <t>Tier 2 - Malawi (Arnold et al. 2020)</t>
         </is>
@@ -11482,7 +11774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11491,13 +11783,14 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="44" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="44" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="55" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11531,37 +11824,52 @@
           <t>Sum (check)</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>Urban (%)</t>
+        </is>
+      </c>
+      <c r="H1" s="13" t="inlineStr">
+        <is>
+          <t>Rural (%)</t>
+        </is>
+      </c>
+      <c r="I1" s="13" t="inlineStr">
+        <is>
+          <t>Sum (check, residence)</t>
+        </is>
+      </c>
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>Source (survey/report)</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="I1" s="6" t="inlineStr">
+      <c r="L1" s="6" t="inlineStr">
         <is>
           <t>Indicator / exact table (lead)</t>
         </is>
       </c>
-      <c r="J1" s="6" t="inlineStr">
+      <c r="M1" s="6" t="inlineStr">
         <is>
           <t>Page / Table no. (to verify)</t>
         </is>
       </c>
-      <c r="K1" s="6" t="inlineStr">
+      <c r="N1" s="6" t="inlineStr">
         <is>
           <t>Justification</t>
         </is>
       </c>
-      <c r="L1" s="6" t="inlineStr">
+      <c r="O1" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="M1" s="13" t="inlineStr">
+      <c r="P1" s="13" t="inlineStr">
         <is>
           <t>Data tier</t>
         </is>
@@ -11587,31 +11895,42 @@
         <f>SUM(A2:E2)</f>
         <v/>
       </c>
-      <c r="G2" s="18" t="inlineStr">
+      <c r="G2" s="20" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="H2" s="20" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="I2">
+        <f>SUM(G2:H2)</f>
+        <v/>
+      </c>
+      <c r="J2" s="18" t="inlineStr">
         <is>
           <t>Arnold, Nkhoma &amp; Griffin (2020), Health Policy and Planning 35(6):646-656, Table 1</t>
         </is>
       </c>
-      <c r="H2" s="7" t="n">
+      <c r="K2" s="7" t="n">
         <v>2020</v>
       </c>
-      <c r="I2" s="19" t="inlineStr">
+      <c r="L2" s="19" t="inlineStr">
         <is>
           <t>Table 1 - % of total health opportunity cost by wealth quintile</t>
         </is>
       </c>
-      <c r="J2" s="10" t="inlineStr"/>
-      <c r="K2" s="19" t="inlineStr">
-        <is>
-          <t>No Senegal all-cause public-sector care-seeking table was found (see earlier search). Malawi's published national opportunity-cost distribution (23/22/20/19/16% from poorest to richest, Table 1) is used directly as the fallback, on the basis that both countries show the same general pattern in every Senegal-sourced care-seeking indicator so far (ANC4, delivery, diarrhea, malaria testing, HIV testing all increase with wealth) — i.e. richer households draw a smaller share of displaced public spending. Replace with an EHCVM-derived figure as soon as accessible (see tab 6).</t>
-        </is>
-      </c>
-      <c r="L2" s="7" t="inlineStr">
+      <c r="M2" s="10" t="inlineStr"/>
+      <c r="N2" s="19" t="inlineStr">
+        <is>
+          <t>No Senegal all-cause public-sector care-seeking table was found (see earlier search). Malawi's published national opportunity-cost distribution (23/22/20/19/16% from poorest to richest, Table 1) is used directly as the fallback, on the basis that both countries show the same general pattern in every Senegal-sourced care-seeking indicator so far (ANC4, delivery, diarrhea, malaria testing, HIV testing all increase with wealth) — i.e. richer households draw a smaller share of displaced public spending. Replace with an EHCVM-derived figure as soon as accessible (see tab 6).
+RESIDENCE (Urban/Rural): Arnold, Nkhoma &amp; Griffin (2020), Table 1 (relative-risk transported to Senegal's own urban/rural population split). Senegal's own urban population share is proxied by the EDS-Continue &lt;5 sample composition (39.6% urban / 60.4% rural, Tables 10.8/10.9); Malawi's opportunity-cost-share/population-share ratio (17%/15%=1.13 urban, 83%/85%=0.98 rural) is applied to it and renormalized to 100%.</t>
+        </is>
+      </c>
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t>Filled</t>
         </is>
       </c>
-      <c r="M2" s="20" t="inlineStr">
+      <c r="P2" s="20" t="inlineStr">
         <is>
           <t>Tier 2 - Malawi (Arnold et al. 2020)</t>
         </is>
@@ -11633,7 +11952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -11719,6 +12038,26 @@
       <c r="D4" s="8" t="inlineStr">
         <is>
           <t>To be tested in sensitivity analysis (e.g. ε=2 and ε=25) once the R coding starts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>National urban population share (%)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Proxy: EDS-Continue Senegal 2023 &lt;5-year-old sample composition (Tables 10.8/10.9: 3,762 urban / 5,743 rural)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Used to weight the urban/rural Atkinson EDE calculation (population is NOT equal between residence groups, unlike wealth quintiles). Replace with the RGPH-5 (2023) census figure when available - this survey-sample proxy is specific to the under-5 population, not the whole population.</t>
         </is>
       </c>
     </row>
